--- a/data/germany/p4_modeling/2024-10-13/df_best_model.xlsx
+++ b/data/germany/p4_modeling/2024-10-13/df_best_model.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,16 +543,16 @@
         <v>2.678358390580665</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8252392950538564</v>
+        <v>0.825239295053857</v>
       </c>
       <c r="D2" t="n">
         <v>2.333350731955595</v>
       </c>
       <c r="E2" t="n">
-        <v>690.2693882971239</v>
+        <v>673.6941953558677</v>
       </c>
       <c r="F2" t="n">
-        <v>4.541245975638973</v>
+        <v>4.346414163586243</v>
       </c>
       <c r="G2" t="n">
         <v>-0.5</v>
@@ -577,7 +577,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>(152, 31)</t>
+          <t>(155, 31)</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -586,54 +586,54 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4.502944422129832</v>
+        <v>4.266853129312737</v>
       </c>
       <c r="O2" t="n">
         <v>61</v>
       </c>
       <c r="P2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="S2" t="n">
         <v>32</v>
       </c>
       <c r="T2" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="U2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="V2" t="n">
-        <v>59.21052631578947</v>
+        <v>58.70967741935483</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>410</v>
+        <v>279</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8712421768898202</v>
+        <v>6.527386367986731</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3027598783600587</v>
+        <v>2.40450836332167</v>
       </c>
       <c r="D3" t="n">
-        <v>1.934022065104386</v>
+        <v>2.204814415892841</v>
       </c>
       <c r="E3" t="n">
-        <v>295.9713768130447</v>
+        <v>542.9782921374516</v>
       </c>
       <c r="F3" t="n">
-        <v>1.947180110612136</v>
+        <v>3.503085755725494</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -655,60 +655,60 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>(152, 33)</t>
+          <t>(155, 21)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>neural_networ</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>5.431433785610267</v>
+        <v>0.4568823336867963</v>
       </c>
       <c r="O3" t="n">
         <v>61</v>
       </c>
       <c r="P3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q3" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R3" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="S3" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="T3" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="U3" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V3" t="n">
-        <v>55.26315789473685</v>
+        <v>54.83870967741935</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>357</v>
+        <v>59</v>
       </c>
       <c r="B4" t="n">
-        <v>0.2370214074239834</v>
+        <v>6.681936560962774</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7085141204278551</v>
+        <v>-0.107961075180348</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7035910574786063</v>
+        <v>1.265521932217489</v>
       </c>
       <c r="E4" t="n">
-        <v>113.5397894843368</v>
+        <v>391.5915480398387</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7469722992390576</v>
+        <v>2.526397084127991</v>
       </c>
       <c r="G4" t="n">
         <v>-0.5</v>
@@ -720,7 +720,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -733,72 +733,72 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>(152, 49)</t>
+          <t>(155, 37)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>neural_networ</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0.05428004566511464</v>
+        <v>24.40099966499655</v>
       </c>
       <c r="O4" t="n">
         <v>61</v>
       </c>
       <c r="P4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R4" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="S4" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="T4" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="U4" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="V4" t="n">
-        <v>56.57894736842105</v>
+        <v>57.41935483870968</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>221</v>
+        <v>344</v>
       </c>
       <c r="B5" t="n">
-        <v>1.478551168289379</v>
+        <v>8.777103003563132</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1518977295927441</v>
+        <v>2.132509287779377</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4684372458790915</v>
+        <v>1.079174411200162</v>
       </c>
       <c r="E5" t="n">
-        <v>75.35280945259021</v>
+        <v>352.1234377525424</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4957421674512514</v>
+        <v>2.271764114532532</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>kelly</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -807,76 +807,76 @@
         </is>
       </c>
       <c r="K5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>(152, 30)</t>
+          <t>(155, 16)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>neural_networ</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>4.263657519966857</v>
+        <v>0.06530092391680194</v>
       </c>
       <c r="O5" t="n">
         <v>61</v>
       </c>
       <c r="P5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R5" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="S5" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="T5" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="U5" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="V5" t="n">
-        <v>50.6578947368421</v>
+        <v>58.06451612903226</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>71</v>
+        <v>213</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8006534525271729</v>
+        <v>1.492212700963593</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1413798776813807</v>
+        <v>1.080505611678709</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3937198933121853</v>
+        <v>1.462907982036795</v>
       </c>
       <c r="E6" t="n">
-        <v>66.73591430781033</v>
+        <v>259.9652808852854</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4390520678145416</v>
+        <v>1.677195360550229</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>kelly</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -885,11 +885,11 @@
         </is>
       </c>
       <c r="K6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>(152, 16)</t>
+          <t>(155, 31)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -898,63 +898,63 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.105477773888068</v>
+        <v>0.5522319758658939</v>
       </c>
       <c r="O6" t="n">
         <v>61</v>
       </c>
       <c r="P6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q6" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R6" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="S6" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="T6" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="U6" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="V6" t="n">
-        <v>55.26315789473685</v>
+        <v>59.35483870967742</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>406</v>
+        <v>335</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2607818755694558</v>
+        <v>1.212172007313326</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1200281091623771</v>
+        <v>0.4745645293740665</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1528509544245408</v>
+        <v>0.4617971516828195</v>
       </c>
       <c r="E7" t="n">
-        <v>53.81452363201117</v>
+        <v>259.6537164277134</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3540429186316524</v>
+        <v>1.67518526727557</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>kelly</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -963,64 +963,64 @@
         </is>
       </c>
       <c r="K7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>(152, 31)</t>
+          <t>(155, 25)</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>neural_networ</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.949666716424685</v>
+        <v>2.529942007012364</v>
       </c>
       <c r="O7" t="n">
         <v>61</v>
       </c>
       <c r="P7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R7" t="n">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="S7" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="T7" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="U7" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="V7" t="n">
-        <v>56.57894736842105</v>
+        <v>52.25806451612903</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>341</v>
+        <v>474</v>
       </c>
       <c r="B8" t="n">
-        <v>0.06273930017235956</v>
+        <v>0.4724061668232272</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1787687467319226</v>
+        <v>0.003714210521516179</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2737920087506086</v>
+        <v>1.434039276393762</v>
       </c>
       <c r="E8" t="n">
-        <v>43.65584984011548</v>
+        <v>212.7421710223927</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2872095384218123</v>
+        <v>1.37253013562834</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5</v>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>(152, 31)</t>
+          <t>(155, 97)</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1054,63 +1054,63 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.6065981536051432</v>
+        <v>368.5348251471915</v>
       </c>
       <c r="O8" t="n">
         <v>61</v>
       </c>
       <c r="P8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R8" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="S8" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="T8" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="U8" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="V8" t="n">
-        <v>52.63157894736842</v>
+        <v>56.7741935483871</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>212</v>
+        <v>57</v>
       </c>
       <c r="B9" t="n">
-        <v>1.055582605379129</v>
+        <v>3.211687804967631</v>
       </c>
       <c r="C9" t="n">
-        <v>0.08866301697994658</v>
+        <v>1.270427704469312</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01203539324716265</v>
+        <v>0.7948919846303321</v>
       </c>
       <c r="E9" t="n">
-        <v>27.24935113669143</v>
+        <v>200.6888918569892</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1792720469519173</v>
+        <v>1.29476704423864</v>
       </c>
       <c r="G9" t="n">
         <v>-0.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>kelly</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1119,64 +1119,64 @@
         </is>
       </c>
       <c r="K9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>(152, 46)</t>
+          <t>(155, 50)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>neural_networ</t>
+          <t>XGBClassifier</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.021948418385811</v>
+        <v>0.01915838239649756</v>
       </c>
       <c r="O9" t="n">
         <v>61</v>
       </c>
       <c r="P9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q9" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R9" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="S9" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="T9" t="n">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="U9" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="V9" t="n">
-        <v>53.28947368421053</v>
+        <v>50.32258064516129</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>277</v>
+        <v>24</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5517919599908921</v>
+        <v>1.789010866372069</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.1260216456898324</v>
+        <v>-0.00379045956092412</v>
       </c>
       <c r="D10" t="n">
-        <v>0.09413751056523419</v>
+        <v>1.087484448236312</v>
       </c>
       <c r="E10" t="n">
-        <v>17.29091335699998</v>
+        <v>167.2902947239339</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1137560089276314</v>
+        <v>1.07929222402538</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5</v>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1201,118 +1201,5812 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>(152, 42)</t>
+          <t>(155, 15)</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>neural_networ</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.902670396858732</v>
+        <v>285.7391475038576</v>
       </c>
       <c r="O10" t="n">
         <v>61</v>
       </c>
       <c r="P10" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q10" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R10" t="n">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="S10" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="U10" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="V10" t="n">
-        <v>53.28947368421053</v>
+        <v>59.35483870967742</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>647</v>
+        <v>96</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5564467589700806</v>
+        <v>2.915593451022245</v>
       </c>
       <c r="C11" t="n">
-        <v>0.03410062533821545</v>
+        <v>0.4235651327288261</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.002853405288390623</v>
+        <v>0.5932649455838136</v>
       </c>
       <c r="E11" t="n">
-        <v>7.272553774718532</v>
+        <v>158.6168442697161</v>
       </c>
       <c r="F11" t="n">
-        <v>0.04784574851788508</v>
+        <v>1.023334479159459</v>
       </c>
       <c r="G11" t="n">
         <v>-0.5</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>(155, 24)</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>1.416002640648458</v>
+      </c>
+      <c r="O11" t="n">
+        <v>61</v>
+      </c>
+      <c r="P11" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>58</v>
+      </c>
+      <c r="R11" t="n">
+        <v>74</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="n">
+        <v>56</v>
+      </c>
+      <c r="U11" t="n">
+        <v>90</v>
+      </c>
+      <c r="V11" t="n">
+        <v>58.06451612903226</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1.342169209103876</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.2762281430763522</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.2839464199470973</v>
+      </c>
+      <c r="E12" t="n">
+        <v>143.0804928967115</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.923099954172332</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>(155, 26)</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>4.341802699362091</v>
+      </c>
+      <c r="O12" t="n">
+        <v>61</v>
+      </c>
+      <c r="P12" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>58</v>
+      </c>
+      <c r="R12" t="n">
+        <v>56</v>
+      </c>
+      <c r="S12" t="n">
+        <v>27</v>
+      </c>
+      <c r="T12" t="n">
+        <v>72</v>
+      </c>
+      <c r="U12" t="n">
+        <v>84</v>
+      </c>
+      <c r="V12" t="n">
+        <v>54.19354838709678</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>221</v>
+      </c>
+      <c r="B13" t="n">
+        <v>3.336238494732197</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.0259237453433272</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.2893145919868438</v>
+      </c>
+      <c r="E13" t="n">
+        <v>134.496286945404</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.867717980292929</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>(155, 30)</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>32.47193736094467</v>
+      </c>
+      <c r="O13" t="n">
+        <v>61</v>
+      </c>
+      <c r="P13" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>58</v>
+      </c>
+      <c r="R13" t="n">
+        <v>72</v>
+      </c>
+      <c r="S13" t="n">
+        <v>32</v>
+      </c>
+      <c r="T13" t="n">
+        <v>51</v>
+      </c>
+      <c r="U13" t="n">
+        <v>86</v>
+      </c>
+      <c r="V13" t="n">
+        <v>55.48387096774194</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>207</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.4233609722271777</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.3773779404424502</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.8933398823573767</v>
+      </c>
+      <c r="E14" t="n">
+        <v>134.2082511489566</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.8658596848319781</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>(155, 13)</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>1.294409905933601</v>
+      </c>
+      <c r="O14" t="n">
+        <v>61</v>
+      </c>
+      <c r="P14" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>58</v>
+      </c>
+      <c r="R14" t="n">
+        <v>86</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="n">
+        <v>54</v>
+      </c>
+      <c r="U14" t="n">
+        <v>91</v>
+      </c>
+      <c r="V14" t="n">
+        <v>58.70967741935483</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>268</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3.993685358122979</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.2117133094619613</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.003906252423939</v>
+      </c>
+      <c r="E15" t="n">
+        <v>132.6178685579126</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.8555991519865331</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K15" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>(155, 46)</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>3.041310176298856</v>
+      </c>
+      <c r="O15" t="n">
+        <v>61</v>
+      </c>
+      <c r="P15" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>58</v>
+      </c>
+      <c r="R15" t="n">
+        <v>71</v>
+      </c>
+      <c r="S15" t="n">
+        <v>17</v>
+      </c>
+      <c r="T15" t="n">
+        <v>67</v>
+      </c>
+      <c r="U15" t="n">
+        <v>88</v>
+      </c>
+      <c r="V15" t="n">
+        <v>56.7741935483871</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>422</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3.410325243804548</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5018011388283881</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.9156651342791016</v>
+      </c>
+      <c r="E16" t="n">
+        <v>129.1473183631979</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.8332085055690189</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>(155, 24)</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>0.6604356608564205</v>
+      </c>
+      <c r="O16" t="n">
+        <v>61</v>
+      </c>
+      <c r="P16" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>58</v>
+      </c>
+      <c r="R16" t="n">
+        <v>86</v>
+      </c>
+      <c r="S16" t="n">
+        <v>13</v>
+      </c>
+      <c r="T16" t="n">
+        <v>56</v>
+      </c>
+      <c r="U16" t="n">
+        <v>90</v>
+      </c>
+      <c r="V16" t="n">
+        <v>58.06451612903226</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-0.01038480462475604</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.5536811842968609</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.3241581938982677</v>
+      </c>
+      <c r="E17" t="n">
+        <v>122.8230420100562</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.7924067226455238</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>(155, 25)</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>2.431160648256142</v>
+      </c>
+      <c r="O17" t="n">
+        <v>61</v>
+      </c>
+      <c r="P17" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>58</v>
+      </c>
+      <c r="R17" t="n">
+        <v>77</v>
+      </c>
+      <c r="S17" t="n">
+        <v>14</v>
+      </c>
+      <c r="T17" t="n">
+        <v>64</v>
+      </c>
+      <c r="U17" t="n">
+        <v>89</v>
+      </c>
+      <c r="V17" t="n">
+        <v>57.41935483870968</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>357</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0.2370214074239831</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7085141204278551</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.7035910574786063</v>
+      </c>
+      <c r="E18" t="n">
+        <v>110.1899876023942</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.7109031458218977</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>(155, 49)</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>0.00337188113145853</v>
+      </c>
+      <c r="O18" t="n">
+        <v>61</v>
+      </c>
+      <c r="P18" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>58</v>
+      </c>
+      <c r="R18" t="n">
+        <v>73</v>
+      </c>
+      <c r="S18" t="n">
+        <v>29</v>
+      </c>
+      <c r="T18" t="n">
+        <v>53</v>
+      </c>
+      <c r="U18" t="n">
+        <v>87</v>
+      </c>
+      <c r="V18" t="n">
+        <v>56.12903225806451</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>211</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-0.7115840249557536</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5020259378717035</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.5982442102095181</v>
+      </c>
+      <c r="E19" t="n">
+        <v>109.4843064352667</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.7063503640984949</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>(155, 46)</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>0.4069997400791832</v>
+      </c>
+      <c r="O19" t="n">
+        <v>61</v>
+      </c>
+      <c r="P19" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>58</v>
+      </c>
+      <c r="R19" t="n">
+        <v>83</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="n">
+        <v>47</v>
+      </c>
+      <c r="U19" t="n">
+        <v>88</v>
+      </c>
+      <c r="V19" t="n">
+        <v>56.7741935483871</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>415</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0.3529634832596187</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.1476246101932787</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.6752390164345956</v>
+      </c>
+      <c r="E20" t="n">
+        <v>99.083641679301</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.6392493011567806</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>(155, 9)</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>5.330235319977057</v>
+      </c>
+      <c r="O20" t="n">
+        <v>61</v>
+      </c>
+      <c r="P20" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>58</v>
+      </c>
+      <c r="R20" t="n">
+        <v>74</v>
+      </c>
+      <c r="S20" t="n">
+        <v>24</v>
+      </c>
+      <c r="T20" t="n">
+        <v>57</v>
+      </c>
+      <c r="U20" t="n">
+        <v>87</v>
+      </c>
+      <c r="V20" t="n">
+        <v>56.12903225806451</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>280</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-0.9995777266755803</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.3027638370462388</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.2031719772130288</v>
+      </c>
+      <c r="E21" t="n">
+        <v>89.92243164915652</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.5801447203171388</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K21" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>(155, 21)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>2.916162531090322</v>
+      </c>
+      <c r="O21" t="n">
+        <v>61</v>
+      </c>
+      <c r="P21" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>58</v>
+      </c>
+      <c r="R21" t="n">
+        <v>70</v>
+      </c>
+      <c r="S21" t="n">
+        <v>63</v>
+      </c>
+      <c r="T21" t="n">
+        <v>22</v>
+      </c>
+      <c r="U21" t="n">
+        <v>76</v>
+      </c>
+      <c r="V21" t="n">
+        <v>49.03225806451613</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0.2350678873774191</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.0573159938124617</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.05909898493825665</v>
+      </c>
+      <c r="E22" t="n">
+        <v>71.02769806895992</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.4582432133481285</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>(155, 31)</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>8.995032151889458</v>
+      </c>
+      <c r="O22" t="n">
+        <v>61</v>
+      </c>
+      <c r="P22" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>58</v>
+      </c>
+      <c r="R22" t="n">
+        <v>53</v>
+      </c>
+      <c r="S22" t="n">
+        <v>14</v>
+      </c>
+      <c r="T22" t="n">
+        <v>88</v>
+      </c>
+      <c r="U22" t="n">
+        <v>75</v>
+      </c>
+      <c r="V22" t="n">
+        <v>48.38709677419355</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>410</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0.4852566975915317</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.1461979692137022</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.5468203847451146</v>
+      </c>
+      <c r="E23" t="n">
+        <v>67.70745837295857</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.4368223120836037</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>(155, 33)</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1.987882215005918</v>
+      </c>
+      <c r="O23" t="n">
+        <v>61</v>
+      </c>
+      <c r="P23" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>58</v>
+      </c>
+      <c r="R23" t="n">
+        <v>72</v>
+      </c>
+      <c r="S23" t="n">
+        <v>36</v>
+      </c>
+      <c r="T23" t="n">
+        <v>47</v>
+      </c>
+      <c r="U23" t="n">
+        <v>81</v>
+      </c>
+      <c r="V23" t="n">
+        <v>52.25806451612903</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>172</v>
+      </c>
+      <c r="B24" t="n">
+        <v>4.007565304834913</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.2964795458012918</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.1088117443174109</v>
+      </c>
+      <c r="E24" t="n">
+        <v>63.457172326277</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.4094011117824323</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K24" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>(155, 25)</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>0.3808747267065208</v>
+      </c>
+      <c r="O24" t="n">
+        <v>61</v>
+      </c>
+      <c r="P24" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>58</v>
+      </c>
+      <c r="R24" t="n">
+        <v>62</v>
+      </c>
+      <c r="S24" t="n">
+        <v>23</v>
+      </c>
+      <c r="T24" t="n">
+        <v>70</v>
+      </c>
+      <c r="U24" t="n">
+        <v>87</v>
+      </c>
+      <c r="V24" t="n">
+        <v>56.12903225806451</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>279</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1.351123566359268</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.1818384287428233</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.07696342694475296</v>
+      </c>
+      <c r="E25" t="n">
+        <v>59.98856093011469</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.3870229737426754</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>(155, 21)</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>1.128389342222306</v>
+      </c>
+      <c r="O25" t="n">
+        <v>61</v>
+      </c>
+      <c r="P25" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>58</v>
+      </c>
+      <c r="R25" t="n">
+        <v>73</v>
+      </c>
+      <c r="S25" t="n">
+        <v>13</v>
+      </c>
+      <c r="T25" t="n">
+        <v>69</v>
+      </c>
+      <c r="U25" t="n">
+        <v>87</v>
+      </c>
+      <c r="V25" t="n">
+        <v>56.12903225806451</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>444</v>
+      </c>
+      <c r="B26" t="n">
+        <v>-0.2243564134479425</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.1782956329442234</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.1885515258241757</v>
+      </c>
+      <c r="E26" t="n">
+        <v>58.80279140007115</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.3793728477423945</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>(155, 56)</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>3.127774199949555</v>
+      </c>
+      <c r="O26" t="n">
+        <v>61</v>
+      </c>
+      <c r="P26" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>58</v>
+      </c>
+      <c r="R26" t="n">
+        <v>88</v>
+      </c>
+      <c r="S26" t="n">
+        <v>21</v>
+      </c>
+      <c r="T26" t="n">
+        <v>46</v>
+      </c>
+      <c r="U26" t="n">
+        <v>86</v>
+      </c>
+      <c r="V26" t="n">
+        <v>55.48387096774194</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>4.475720318689337</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.2413123311822595</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.0331108230031946</v>
+      </c>
+      <c r="E27" t="n">
+        <v>57.12218852791716</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.3685302485672075</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K27" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>(155, 25)</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>0.5271919456484893</v>
+      </c>
+      <c r="O27" t="n">
+        <v>61</v>
+      </c>
+      <c r="P27" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>58</v>
+      </c>
+      <c r="R27" t="n">
+        <v>75</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="n">
+        <v>65</v>
+      </c>
+      <c r="U27" t="n">
+        <v>88</v>
+      </c>
+      <c r="V27" t="n">
+        <v>56.7741935483871</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>71</v>
+      </c>
+      <c r="B28" t="n">
+        <v>0.8557506336127091</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.1644726822817614</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.4158870792286541</v>
+      </c>
+      <c r="E28" t="n">
+        <v>55.93999180644226</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.3609031729447888</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>(155, 16)</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>1.194304658609011</v>
+      </c>
+      <c r="O28" t="n">
+        <v>61</v>
+      </c>
+      <c r="P28" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>58</v>
+      </c>
+      <c r="R28" t="n">
+        <v>62</v>
+      </c>
+      <c r="S28" t="n">
+        <v>34</v>
+      </c>
+      <c r="T28" t="n">
+        <v>59</v>
+      </c>
+      <c r="U28" t="n">
+        <v>86</v>
+      </c>
+      <c r="V28" t="n">
+        <v>55.48387096774194</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>392</v>
+      </c>
+      <c r="B29" t="n">
+        <v>-0.1086907760889773</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.03822393906873231</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.1804562135608609</v>
+      </c>
+      <c r="E29" t="n">
+        <v>55.19867956054634</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.3561205132938474</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>(155, 9)</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>10.31668797016157</v>
+      </c>
+      <c r="O29" t="n">
+        <v>61</v>
+      </c>
+      <c r="P29" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>58</v>
+      </c>
+      <c r="R29" t="n">
+        <v>61</v>
+      </c>
+      <c r="S29" t="n">
+        <v>42</v>
+      </c>
+      <c r="T29" t="n">
+        <v>52</v>
+      </c>
+      <c r="U29" t="n">
+        <v>83</v>
+      </c>
+      <c r="V29" t="n">
+        <v>53.5483870967742</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>498</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0.4157961683273843</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.3168617114475185</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.4903710704283664</v>
+      </c>
+      <c r="E30" t="n">
+        <v>50.27426369231372</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.3243500883375079</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K30" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>(155, 97)</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>0.02363294970471581</v>
+      </c>
+      <c r="O30" t="n">
+        <v>61</v>
+      </c>
+      <c r="P30" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>58</v>
+      </c>
+      <c r="R30" t="n">
+        <v>77</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="n">
+        <v>58</v>
+      </c>
+      <c r="U30" t="n">
+        <v>86</v>
+      </c>
+      <c r="V30" t="n">
+        <v>55.48387096774194</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>421</v>
+      </c>
+      <c r="B31" t="n">
+        <v>0.1454038283642836</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.03085299292867773</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.1745018784928799</v>
+      </c>
+      <c r="E31" t="n">
+        <v>45.81457397667549</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.2955778966237129</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K31" t="b">
+        <v>1</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>(155, 24)</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>8.580201742728642</v>
+      </c>
+      <c r="O31" t="n">
+        <v>61</v>
+      </c>
+      <c r="P31" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>58</v>
+      </c>
+      <c r="R31" t="n">
+        <v>72</v>
+      </c>
+      <c r="S31" t="n">
+        <v>60</v>
+      </c>
+      <c r="T31" t="n">
+        <v>23</v>
+      </c>
+      <c r="U31" t="n">
+        <v>77</v>
+      </c>
+      <c r="V31" t="n">
+        <v>49.67741935483871</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>436</v>
+      </c>
+      <c r="B32" t="n">
+        <v>-0.008497856212409829</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.003426069430821883</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.120686122006</v>
+      </c>
+      <c r="E32" t="n">
+        <v>45.6675434093053</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.2946293123180987</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>(155, 41)</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>86.99630517336591</v>
+      </c>
+      <c r="O32" t="n">
+        <v>61</v>
+      </c>
+      <c r="P32" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>58</v>
+      </c>
+      <c r="R32" t="n">
+        <v>71</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="n">
+        <v>59</v>
+      </c>
+      <c r="U32" t="n">
+        <v>86</v>
+      </c>
+      <c r="V32" t="n">
+        <v>55.48387096774194</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>477</v>
+      </c>
+      <c r="B33" t="n">
+        <v>0.2414435616335453</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.03597214731369689</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.04201263125913859</v>
+      </c>
+      <c r="E33" t="n">
+        <v>44.6028770540014</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.2877604971225897</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K33" t="b">
+        <v>1</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>(155, 49)</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>8.999536269357513</v>
+      </c>
+      <c r="O33" t="n">
+        <v>61</v>
+      </c>
+      <c r="P33" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>58</v>
+      </c>
+      <c r="R33" t="n">
+        <v>46</v>
+      </c>
+      <c r="S33" t="n">
+        <v>59</v>
+      </c>
+      <c r="T33" t="n">
+        <v>50</v>
+      </c>
+      <c r="U33" t="n">
+        <v>76</v>
+      </c>
+      <c r="V33" t="n">
+        <v>49.03225806451613</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>406</v>
+      </c>
+      <c r="B34" t="n">
+        <v>0.2848935796357853</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.1351202142408212</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.1315953457372646</v>
+      </c>
+      <c r="E34" t="n">
+        <v>43.30078333570057</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.2793598924883908</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K34" t="b">
+        <v>1</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>(155, 31)</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>1.067491485696544</v>
+      </c>
+      <c r="O34" t="n">
+        <v>61</v>
+      </c>
+      <c r="P34" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>58</v>
+      </c>
+      <c r="R34" t="n">
+        <v>72</v>
+      </c>
+      <c r="S34" t="n">
+        <v>30</v>
+      </c>
+      <c r="T34" t="n">
+        <v>53</v>
+      </c>
+      <c r="U34" t="n">
+        <v>87</v>
+      </c>
+      <c r="V34" t="n">
+        <v>56.12903225806451</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>341</v>
+      </c>
+      <c r="B35" t="n">
+        <v>0.06302463003953875</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.1780940794900145</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.2747934558655451</v>
+      </c>
+      <c r="E35" t="n">
+        <v>37.00127863161325</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.2387179266555693</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>(155, 31)</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>0.3404034953837635</v>
+      </c>
+      <c r="O35" t="n">
+        <v>61</v>
+      </c>
+      <c r="P35" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>58</v>
+      </c>
+      <c r="R35" t="n">
+        <v>56</v>
+      </c>
+      <c r="S35" t="n">
+        <v>36</v>
+      </c>
+      <c r="T35" t="n">
+        <v>63</v>
+      </c>
+      <c r="U35" t="n">
+        <v>81</v>
+      </c>
+      <c r="V35" t="n">
+        <v>52.25806451612903</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>334</v>
+      </c>
+      <c r="B36" t="n">
+        <v>0.4546497175910247</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.06598256932761686</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.08499720844968882</v>
+      </c>
+      <c r="E36" t="n">
+        <v>36.74986032095575</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.2370958730384242</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K36" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>(155, 49)</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>2.593310710002743</v>
+      </c>
+      <c r="O36" t="n">
+        <v>61</v>
+      </c>
+      <c r="P36" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>58</v>
+      </c>
+      <c r="R36" t="n">
+        <v>71</v>
+      </c>
+      <c r="S36" t="n">
+        <v>14</v>
+      </c>
+      <c r="T36" t="n">
+        <v>70</v>
+      </c>
+      <c r="U36" t="n">
+        <v>87</v>
+      </c>
+      <c r="V36" t="n">
+        <v>56.12903225806451</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>212</v>
+      </c>
+      <c r="B37" t="n">
+        <v>0.8248242484767542</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.0105665406854115</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-0.05520295180197195</v>
+      </c>
+      <c r="E37" t="n">
+        <v>31.99004474116876</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.2063873854268952</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K37" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>(155, 46)</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>20.53216209273109</v>
+      </c>
+      <c r="O37" t="n">
+        <v>61</v>
+      </c>
+      <c r="P37" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>58</v>
+      </c>
+      <c r="R37" t="n">
+        <v>59</v>
+      </c>
+      <c r="S37" t="n">
+        <v>38</v>
+      </c>
+      <c r="T37" t="n">
+        <v>58</v>
+      </c>
+      <c r="U37" t="n">
+        <v>81</v>
+      </c>
+      <c r="V37" t="n">
+        <v>52.25806451612903</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>248</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1.099932385944462</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.1182431950409602</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-0.05177219699162777</v>
+      </c>
+      <c r="E38" t="n">
+        <v>30.975426273491</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.1998414598289742</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K38" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>(155, 17)</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>2.690088463524245</v>
+      </c>
+      <c r="O38" t="n">
+        <v>61</v>
+      </c>
+      <c r="P38" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>58</v>
+      </c>
+      <c r="R38" t="n">
+        <v>74</v>
+      </c>
+      <c r="S38" t="n">
+        <v>16</v>
+      </c>
+      <c r="T38" t="n">
+        <v>65</v>
+      </c>
+      <c r="U38" t="n">
+        <v>86</v>
+      </c>
+      <c r="V38" t="n">
+        <v>55.48387096774194</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>343</v>
+      </c>
+      <c r="B39" t="n">
+        <v>0.2921060815588314</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.1427123758429452</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.1268154827747561</v>
+      </c>
+      <c r="E39" t="n">
+        <v>29.42355479786201</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.1898293857926581</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K39" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>(155, 16)</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>0.3301536371419188</v>
+      </c>
+      <c r="O39" t="n">
+        <v>61</v>
+      </c>
+      <c r="P39" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>58</v>
+      </c>
+      <c r="R39" t="n">
+        <v>62</v>
+      </c>
+      <c r="S39" t="n">
+        <v>27</v>
+      </c>
+      <c r="T39" t="n">
+        <v>66</v>
+      </c>
+      <c r="U39" t="n">
+        <v>85</v>
+      </c>
+      <c r="V39" t="n">
+        <v>54.83870967741935</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>425</v>
+      </c>
+      <c r="B40" t="n">
+        <v>0.5633294754878193</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.1692830206933624</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-0.06498267093827527</v>
+      </c>
+      <c r="E40" t="n">
+        <v>29.39461357578977</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.1896426682309018</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K40" t="b">
+        <v>0</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>(155, 61)</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>0.1202698738133851</v>
+      </c>
+      <c r="O40" t="n">
+        <v>61</v>
+      </c>
+      <c r="P40" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>58</v>
+      </c>
+      <c r="R40" t="n">
+        <v>35</v>
+      </c>
+      <c r="S40" t="n">
+        <v>61</v>
+      </c>
+      <c r="T40" t="n">
+        <v>59</v>
+      </c>
+      <c r="U40" t="n">
+        <v>75</v>
+      </c>
+      <c r="V40" t="n">
+        <v>48.38709677419355</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>159</v>
+      </c>
+      <c r="B41" t="n">
+        <v>0.0217072053758838</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.001860451894157222</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.03595036498835062</v>
+      </c>
+      <c r="E41" t="n">
+        <v>25.07909137854745</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.1618005895390158</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K41" t="b">
+        <v>1</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>(155, 11)</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>85.96843495236452</v>
+      </c>
+      <c r="O41" t="n">
+        <v>61</v>
+      </c>
+      <c r="P41" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>58</v>
+      </c>
+      <c r="R41" t="n">
+        <v>82</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="n">
+        <v>63</v>
+      </c>
+      <c r="U41" t="n">
+        <v>88</v>
+      </c>
+      <c r="V41" t="n">
+        <v>56.7741935483871</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="B42" t="n">
+        <v>0.8310437370581218</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-0.0666945427329486</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.1507238566715178</v>
+      </c>
+      <c r="E42" t="n">
+        <v>22.38514281399257</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.1444202762193069</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K42" t="b">
+        <v>1</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>(155, 58)</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>3.16539870132373</v>
+      </c>
+      <c r="O42" t="n">
+        <v>61</v>
+      </c>
+      <c r="P42" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>58</v>
+      </c>
+      <c r="R42" t="n">
+        <v>77</v>
+      </c>
+      <c r="S42" t="n">
+        <v>20</v>
+      </c>
+      <c r="T42" t="n">
+        <v>58</v>
+      </c>
+      <c r="U42" t="n">
+        <v>86</v>
+      </c>
+      <c r="V42" t="n">
+        <v>55.48387096774194</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>117</v>
+      </c>
+      <c r="B43" t="n">
+        <v>0.07447120934610041</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.4718767366942926</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-0.1071956178375273</v>
+      </c>
+      <c r="E43" t="n">
+        <v>22.35874250298677</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.1442499516321727</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K43" t="b">
+        <v>1</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>(155, 49)</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>1.305694136656764</v>
+      </c>
+      <c r="O43" t="n">
+        <v>61</v>
+      </c>
+      <c r="P43" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>58</v>
+      </c>
+      <c r="R43" t="n">
+        <v>63</v>
+      </c>
+      <c r="S43" t="n">
+        <v>20</v>
+      </c>
+      <c r="T43" t="n">
+        <v>72</v>
+      </c>
+      <c r="U43" t="n">
+        <v>83</v>
+      </c>
+      <c r="V43" t="n">
+        <v>53.5483870967742</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>358</v>
+      </c>
+      <c r="B44" t="n">
+        <v>0.6674476915393968</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.07143425244537369</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.1413301693072427</v>
+      </c>
+      <c r="E44" t="n">
+        <v>21.98577917233455</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.1418437365957068</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K44" t="b">
+        <v>1</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>(155, 49)</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>0.9856543848369623</v>
+      </c>
+      <c r="O44" t="n">
+        <v>61</v>
+      </c>
+      <c r="P44" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>58</v>
+      </c>
+      <c r="R44" t="n">
+        <v>83</v>
+      </c>
+      <c r="S44" t="n">
+        <v>13</v>
+      </c>
+      <c r="T44" t="n">
+        <v>59</v>
+      </c>
+      <c r="U44" t="n">
+        <v>88</v>
+      </c>
+      <c r="V44" t="n">
+        <v>56.7741935483871</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>361</v>
+      </c>
+      <c r="B45" t="n">
+        <v>0.8201864324123329</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.0724928654458688</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.01454415780694688</v>
+      </c>
+      <c r="E45" t="n">
+        <v>21.60009409778888</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.1393554457921863</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K45" t="b">
+        <v>0</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>(155, 31)</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>0.9223332521769958</v>
+      </c>
+      <c r="O45" t="n">
+        <v>61</v>
+      </c>
+      <c r="P45" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>58</v>
+      </c>
+      <c r="R45" t="n">
+        <v>68</v>
+      </c>
+      <c r="S45" t="n">
+        <v>30</v>
+      </c>
+      <c r="T45" t="n">
+        <v>57</v>
+      </c>
+      <c r="U45" t="n">
+        <v>81</v>
+      </c>
+      <c r="V45" t="n">
+        <v>52.25806451612903</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>274</v>
+      </c>
+      <c r="B46" t="n">
+        <v>-0.6001172288613656</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-0.3381925962621388</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.0700202852432443</v>
+      </c>
+      <c r="E46" t="n">
+        <v>18.96116015603241</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.1223300655227897</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K46" t="b">
+        <v>1</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>(155, 83)</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>1.361717160206457</v>
+      </c>
+      <c r="O46" t="n">
+        <v>61</v>
+      </c>
+      <c r="P46" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>58</v>
+      </c>
+      <c r="R46" t="n">
+        <v>76</v>
+      </c>
+      <c r="S46" t="n">
+        <v>30</v>
+      </c>
+      <c r="T46" t="n">
+        <v>49</v>
+      </c>
+      <c r="U46" t="n">
+        <v>84</v>
+      </c>
+      <c r="V46" t="n">
+        <v>54.19354838709678</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>292</v>
+      </c>
+      <c r="B47" t="n">
+        <v>-0.3535873059946888</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-0.2485668694226605</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.00528265807690057</v>
+      </c>
+      <c r="E47" t="n">
+        <v>18.9168312988632</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.1220440728958916</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K47" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>(155, 45)</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>1.490990907916892</v>
+      </c>
+      <c r="O47" t="n">
+        <v>61</v>
+      </c>
+      <c r="P47" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>58</v>
+      </c>
+      <c r="R47" t="n">
+        <v>62</v>
+      </c>
+      <c r="S47" t="n">
+        <v>43</v>
+      </c>
+      <c r="T47" t="n">
+        <v>50</v>
+      </c>
+      <c r="U47" t="n">
+        <v>80</v>
+      </c>
+      <c r="V47" t="n">
+        <v>51.61290322580645</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>572</v>
+      </c>
+      <c r="B48" t="n">
+        <v>0.5242632072634763</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.04007214459725304</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.1175857062151201</v>
+      </c>
+      <c r="E48" t="n">
+        <v>18.02400720691914</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.1162839174639944</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K48" t="b">
+        <v>1</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>(155, 16)</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>1.9018640911963</v>
+      </c>
+      <c r="O48" t="n">
+        <v>61</v>
+      </c>
+      <c r="P48" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>58</v>
+      </c>
+      <c r="R48" t="n">
+        <v>76</v>
+      </c>
+      <c r="S48" t="n">
+        <v>14</v>
+      </c>
+      <c r="T48" t="n">
+        <v>65</v>
+      </c>
+      <c r="U48" t="n">
+        <v>86</v>
+      </c>
+      <c r="V48" t="n">
+        <v>55.48387096774194</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>580</v>
+      </c>
+      <c r="B49" t="n">
+        <v>0.4634990585950291</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-0.07459878695510624</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.04303934540725303</v>
+      </c>
+      <c r="E49" t="n">
+        <v>17.40973511166827</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.1123208716881824</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K49" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>(155, 7)</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>2.505666194756992</v>
+      </c>
+      <c r="O49" t="n">
+        <v>61</v>
+      </c>
+      <c r="P49" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>58</v>
+      </c>
+      <c r="R49" t="n">
+        <v>69</v>
+      </c>
+      <c r="S49" t="n">
+        <v>20</v>
+      </c>
+      <c r="T49" t="n">
+        <v>66</v>
+      </c>
+      <c r="U49" t="n">
+        <v>86</v>
+      </c>
+      <c r="V49" t="n">
+        <v>55.48387096774194</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>429</v>
+      </c>
+      <c r="B50" t="n">
+        <v>0.3571497128897133</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.01653906194726318</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.01505331774793063</v>
+      </c>
+      <c r="E50" t="n">
+        <v>16.6461387726556</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.1073944436945523</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K50" t="b">
+        <v>0</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>(155, 31)</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>7.493381791361118</v>
+      </c>
+      <c r="O50" t="n">
+        <v>61</v>
+      </c>
+      <c r="P50" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>58</v>
+      </c>
+      <c r="R50" t="n">
+        <v>64</v>
+      </c>
+      <c r="S50" t="n">
+        <v>21</v>
+      </c>
+      <c r="T50" t="n">
+        <v>70</v>
+      </c>
+      <c r="U50" t="n">
+        <v>84</v>
+      </c>
+      <c r="V50" t="n">
+        <v>54.19354838709678</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>277</v>
+      </c>
+      <c r="B51" t="n">
+        <v>0.5517919599908927</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.1260216456898325</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.09413751056523419</v>
+      </c>
+      <c r="E51" t="n">
+        <v>15.90215137832901</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.1025945250214775</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K51" t="b">
+        <v>1</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>(155, 42)</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>1.814102406454726</v>
+      </c>
+      <c r="O51" t="n">
+        <v>61</v>
+      </c>
+      <c r="P51" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>58</v>
+      </c>
+      <c r="R51" t="n">
+        <v>62</v>
+      </c>
+      <c r="S51" t="n">
+        <v>35</v>
+      </c>
+      <c r="T51" t="n">
+        <v>58</v>
+      </c>
+      <c r="U51" t="n">
+        <v>82</v>
+      </c>
+      <c r="V51" t="n">
+        <v>52.90322580645162</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>146</v>
+      </c>
+      <c r="B52" t="n">
+        <v>0.2780184984517027</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.1834947780653825</v>
+      </c>
+      <c r="D52" t="n">
+        <v>-0.06860956031380643</v>
+      </c>
+      <c r="E52" t="n">
+        <v>15.41962023802526</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.09948142089048556</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K52" t="b">
+        <v>0</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>(155, 33)</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>1.542148512013996</v>
+      </c>
+      <c r="O52" t="n">
+        <v>61</v>
+      </c>
+      <c r="P52" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>58</v>
+      </c>
+      <c r="R52" t="n">
+        <v>68</v>
+      </c>
+      <c r="S52" t="n">
+        <v>37</v>
+      </c>
+      <c r="T52" t="n">
+        <v>50</v>
+      </c>
+      <c r="U52" t="n">
+        <v>74</v>
+      </c>
+      <c r="V52" t="n">
+        <v>47.74193548387097</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="n">
+        <v>0.7064682433004293</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.04429165120690385</v>
+      </c>
+      <c r="D53" t="n">
+        <v>-0.02258027658818302</v>
+      </c>
+      <c r="E53" t="n">
+        <v>14.01577206831733</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.09042433592462797</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K53" t="b">
+        <v>1</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>(155, 26)</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>1.041566152099863</v>
+      </c>
+      <c r="O53" t="n">
+        <v>61</v>
+      </c>
+      <c r="P53" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>58</v>
+      </c>
+      <c r="R53" t="n">
+        <v>79</v>
+      </c>
+      <c r="S53" t="n">
+        <v>23</v>
+      </c>
+      <c r="T53" t="n">
+        <v>53</v>
+      </c>
+      <c r="U53" t="n">
+        <v>86</v>
+      </c>
+      <c r="V53" t="n">
+        <v>55.48387096774194</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="B54" t="n">
+        <v>-0.3852820867262662</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.09146384789636997</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.09528949960724332</v>
+      </c>
+      <c r="E54" t="n">
+        <v>12.49025202421622</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.0805822711239756</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K54" t="b">
+        <v>1</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>(155, 31)</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>1.881028657522441</v>
+      </c>
+      <c r="O54" t="n">
+        <v>61</v>
+      </c>
+      <c r="P54" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>58</v>
+      </c>
+      <c r="R54" t="n">
+        <v>78</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="n">
+        <v>52</v>
+      </c>
+      <c r="U54" t="n">
+        <v>86</v>
+      </c>
+      <c r="V54" t="n">
+        <v>55.48387096774194</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>170</v>
+      </c>
+      <c r="B55" t="n">
+        <v>-0.1029400856963792</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.05530706540981128</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.09448713496133204</v>
+      </c>
+      <c r="E55" t="n">
+        <v>12.36282270309107</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.07976014647155528</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" t="b">
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K55" t="b">
         <v>0</v>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>(152, 39)</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>(155, 34)</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>0.4421330417832313</v>
+      </c>
+      <c r="O55" t="n">
+        <v>61</v>
+      </c>
+      <c r="P55" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>58</v>
+      </c>
+      <c r="R55" t="n">
+        <v>75</v>
+      </c>
+      <c r="S55" t="n">
+        <v>64</v>
+      </c>
+      <c r="T55" t="n">
+        <v>16</v>
+      </c>
+      <c r="U55" t="n">
+        <v>72</v>
+      </c>
+      <c r="V55" t="n">
+        <v>46.45161290322581</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>143</v>
+      </c>
+      <c r="B56" t="n">
+        <v>-0.1201471528816287</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-0.02814330236188155</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.04699855476631049</v>
+      </c>
+      <c r="E56" t="n">
+        <v>12.23204601227975</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.07891642588567582</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K56" t="b">
+        <v>0</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>(155, 25)</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>3.804092599757002</v>
+      </c>
+      <c r="O56" t="n">
+        <v>61</v>
+      </c>
+      <c r="P56" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>58</v>
+      </c>
+      <c r="R56" t="n">
+        <v>68</v>
+      </c>
+      <c r="S56" t="n">
+        <v>64</v>
+      </c>
+      <c r="T56" t="n">
+        <v>23</v>
+      </c>
+      <c r="U56" t="n">
+        <v>73</v>
+      </c>
+      <c r="V56" t="n">
+        <v>47.09677419354838</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B57" t="n">
+        <v>1.211317942440521</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-0.1597492412364233</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-0.03469393772447196</v>
+      </c>
+      <c r="E57" t="n">
+        <v>11.98127034129114</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.07729851833091056</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K57" t="b">
+        <v>0</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>(155, 17)</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>1.483874087492606</v>
+      </c>
+      <c r="O57" t="n">
+        <v>61</v>
+      </c>
+      <c r="P57" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>58</v>
+      </c>
+      <c r="R57" t="n">
+        <v>71</v>
+      </c>
+      <c r="S57" t="n">
+        <v>22</v>
+      </c>
+      <c r="T57" t="n">
+        <v>62</v>
+      </c>
+      <c r="U57" t="n">
+        <v>80</v>
+      </c>
+      <c r="V57" t="n">
+        <v>51.61290322580645</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="B58" t="n">
+        <v>0.0539351841503472</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-0.0573988978800277</v>
+      </c>
+      <c r="D58" t="n">
+        <v>-0.05522007788696073</v>
+      </c>
+      <c r="E58" t="n">
+        <v>11.88596389915281</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.0766836380590504</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K58" t="b">
+        <v>0</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>(155, 45)</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t>LogisticRegression</t>
         </is>
       </c>
-      <c r="N11" t="n">
-        <v>0.4030753994492272</v>
-      </c>
-      <c r="O11" t="n">
-        <v>61</v>
-      </c>
-      <c r="P11" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>57</v>
-      </c>
-      <c r="R11" t="n">
+      <c r="N58" t="n">
+        <v>2.335977534260862</v>
+      </c>
+      <c r="O58" t="n">
+        <v>61</v>
+      </c>
+      <c r="P58" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>58</v>
+      </c>
+      <c r="R58" t="n">
         <v>60</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S58" t="n">
+        <v>58</v>
+      </c>
+      <c r="T58" t="n">
+        <v>37</v>
+      </c>
+      <c r="U58" t="n">
+        <v>64</v>
+      </c>
+      <c r="V58" t="n">
+        <v>41.29032258064516</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>430</v>
+      </c>
+      <c r="B59" t="n">
+        <v>-0.1577560146432512</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.06684388437999061</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.01625064721487822</v>
+      </c>
+      <c r="E59" t="n">
+        <v>11.63666026019044</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.07507522748509961</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K59" t="b">
+        <v>0</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>(155, 31)</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>2.123142800294427</v>
+      </c>
+      <c r="O59" t="n">
+        <v>61</v>
+      </c>
+      <c r="P59" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>58</v>
+      </c>
+      <c r="R59" t="n">
+        <v>76</v>
+      </c>
+      <c r="S59" t="n">
+        <v>64</v>
+      </c>
+      <c r="T59" t="n">
+        <v>15</v>
+      </c>
+      <c r="U59" t="n">
+        <v>65</v>
+      </c>
+      <c r="V59" t="n">
+        <v>41.93548387096774</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>378</v>
+      </c>
+      <c r="B60" t="n">
+        <v>0.2788183951868297</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-0.01338843628638955</v>
+      </c>
+      <c r="D60" t="n">
+        <v>-0.1637146389495513</v>
+      </c>
+      <c r="E60" t="n">
+        <v>11.35917064892723</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.07328497192856279</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K60" t="b">
+        <v>1</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>(155, 59)</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>6.473751404640362</v>
+      </c>
+      <c r="O60" t="n">
+        <v>61</v>
+      </c>
+      <c r="P60" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>58</v>
+      </c>
+      <c r="R60" t="n">
+        <v>81</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="n">
+        <v>64</v>
+      </c>
+      <c r="U60" t="n">
+        <v>86</v>
+      </c>
+      <c r="V60" t="n">
+        <v>55.48387096774194</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>548</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1.053228190271549</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.03188414292353826</v>
+      </c>
+      <c r="D61" t="n">
+        <v>-0.06150005562551759</v>
+      </c>
+      <c r="E61" t="n">
+        <v>9.970410191270716</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.06432522704045623</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K61" t="b">
+        <v>1</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>(155, 15)</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>1.017467654523922</v>
+      </c>
+      <c r="O61" t="n">
+        <v>61</v>
+      </c>
+      <c r="P61" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>58</v>
+      </c>
+      <c r="R61" t="n">
+        <v>69</v>
+      </c>
+      <c r="S61" t="n">
+        <v>21</v>
+      </c>
+      <c r="T61" t="n">
+        <v>65</v>
+      </c>
+      <c r="U61" t="n">
+        <v>86</v>
+      </c>
+      <c r="V61" t="n">
+        <v>55.48387096774194</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>412</v>
+      </c>
+      <c r="B62" t="n">
+        <v>-0.08348558308319809</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-0.1430934428906292</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.07863894736605176</v>
+      </c>
+      <c r="E62" t="n">
+        <v>9.866304548598919</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.06365357773289625</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K62" t="b">
+        <v>1</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>(155, 25)</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>1.444839235446649</v>
+      </c>
+      <c r="O62" t="n">
+        <v>61</v>
+      </c>
+      <c r="P62" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>58</v>
+      </c>
+      <c r="R62" t="n">
+        <v>80</v>
+      </c>
+      <c r="S62" t="n">
+        <v>14</v>
+      </c>
+      <c r="T62" t="n">
+        <v>61</v>
+      </c>
+      <c r="U62" t="n">
+        <v>86</v>
+      </c>
+      <c r="V62" t="n">
+        <v>55.48387096774194</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>535</v>
+      </c>
+      <c r="B63" t="n">
+        <v>-0.0906333054743601</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-0.08778486531165526</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.01908738342602201</v>
+      </c>
+      <c r="E63" t="n">
+        <v>9.111691519296798</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.05878510657610837</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K63" t="b">
+        <v>1</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>(155, 32)</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>1.669649675572304</v>
+      </c>
+      <c r="O63" t="n">
+        <v>61</v>
+      </c>
+      <c r="P63" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>58</v>
+      </c>
+      <c r="R63" t="n">
+        <v>78</v>
+      </c>
+      <c r="S63" t="n">
+        <v>21</v>
+      </c>
+      <c r="T63" t="n">
+        <v>56</v>
+      </c>
+      <c r="U63" t="n">
+        <v>86</v>
+      </c>
+      <c r="V63" t="n">
+        <v>55.48387096774194</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>647</v>
+      </c>
+      <c r="B64" t="n">
+        <v>0.6536712781158258</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.01421540720019195</v>
+      </c>
+      <c r="D64" t="n">
+        <v>-0.03454246598539252</v>
+      </c>
+      <c r="E64" t="n">
+        <v>8.376181927219591</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.05403988340141672</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K64" t="b">
+        <v>0</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>(155, 39)</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>4.80150090956853</v>
+      </c>
+      <c r="O64" t="n">
+        <v>61</v>
+      </c>
+      <c r="P64" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>58</v>
+      </c>
+      <c r="R64" t="n">
+        <v>61</v>
+      </c>
+      <c r="S64" t="n">
         <v>39</v>
       </c>
-      <c r="T11" t="n">
-        <v>53</v>
-      </c>
-      <c r="U11" t="n">
+      <c r="T64" t="n">
+        <v>55</v>
+      </c>
+      <c r="U64" t="n">
+        <v>71</v>
+      </c>
+      <c r="V64" t="n">
+        <v>45.80645161290322</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>365</v>
+      </c>
+      <c r="B65" t="n">
+        <v>-0.1461814093818893</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-0.05619148474832798</v>
+      </c>
+      <c r="D65" t="n">
+        <v>-0.01427870100295195</v>
+      </c>
+      <c r="E65" t="n">
+        <v>7.509222893581892</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.04844659931343157</v>
+      </c>
+      <c r="G65" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K65" t="b">
+        <v>0</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>(155, 16)</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>1.86216976701035</v>
+      </c>
+      <c r="O65" t="n">
+        <v>61</v>
+      </c>
+      <c r="P65" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>58</v>
+      </c>
+      <c r="R65" t="n">
+        <v>66</v>
+      </c>
+      <c r="S65" t="n">
+        <v>48</v>
+      </c>
+      <c r="T65" t="n">
+        <v>41</v>
+      </c>
+      <c r="U65" t="n">
+        <v>78</v>
+      </c>
+      <c r="V65" t="n">
+        <v>50.32258064516129</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>621</v>
+      </c>
+      <c r="B66" t="n">
+        <v>-0.1415953479777795</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-0.1951428579239816</v>
+      </c>
+      <c r="D66" t="n">
+        <v>-0.03448641105389612</v>
+      </c>
+      <c r="E66" t="n">
+        <v>7.48892039857553</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.04831561547468084</v>
+      </c>
+      <c r="G66" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K66" t="b">
+        <v>0</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>(155, 56)</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>1.247591000709348</v>
+      </c>
+      <c r="O66" t="n">
+        <v>61</v>
+      </c>
+      <c r="P66" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>58</v>
+      </c>
+      <c r="R66" t="n">
+        <v>77</v>
+      </c>
+      <c r="S66" t="n">
+        <v>64</v>
+      </c>
+      <c r="T66" t="n">
+        <v>14</v>
+      </c>
+      <c r="U66" t="n">
+        <v>66</v>
+      </c>
+      <c r="V66" t="n">
+        <v>42.58064516129032</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>365</v>
+      </c>
+      <c r="B67" t="n">
+        <v>0.1579527099180049</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.01795334593467985</v>
+      </c>
+      <c r="D67" t="n">
+        <v>-0.07962732637621599</v>
+      </c>
+      <c r="E67" t="n">
+        <v>6.809890015605731</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.04393477429423052</v>
+      </c>
+      <c r="G67" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K67" t="b">
+        <v>0</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>(155, 16)</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>1.447163579094372</v>
+      </c>
+      <c r="O67" t="n">
+        <v>61</v>
+      </c>
+      <c r="P67" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>58</v>
+      </c>
+      <c r="R67" t="n">
+        <v>47</v>
+      </c>
+      <c r="S67" t="n">
+        <v>50</v>
+      </c>
+      <c r="T67" t="n">
+        <v>58</v>
+      </c>
+      <c r="U67" t="n">
+        <v>73</v>
+      </c>
+      <c r="V67" t="n">
+        <v>47.09677419354838</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>407</v>
+      </c>
+      <c r="B68" t="n">
+        <v>-0.4431210821438356</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-0.008850954936518747</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.09665265931805246</v>
+      </c>
+      <c r="E68" t="n">
+        <v>6.807723435804817</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.04392079636003108</v>
+      </c>
+      <c r="G68" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K68" t="b">
+        <v>0</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>(155, 16)</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>5.962266407979926</v>
+      </c>
+      <c r="O68" t="n">
+        <v>61</v>
+      </c>
+      <c r="P68" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>58</v>
+      </c>
+      <c r="R68" t="n">
+        <v>84</v>
+      </c>
+      <c r="S68" t="n">
+        <v>58</v>
+      </c>
+      <c r="T68" t="n">
+        <v>13</v>
+      </c>
+      <c r="U68" t="n">
+        <v>71</v>
+      </c>
+      <c r="V68" t="n">
+        <v>45.80645161290322</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>214</v>
+      </c>
+      <c r="B69" t="n">
+        <v>0.3232755595543807</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-0.04340748702347867</v>
+      </c>
+      <c r="D69" t="n">
+        <v>-0.0002025791625736891</v>
+      </c>
+      <c r="E69" t="n">
+        <v>6.118975039465369</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.03947725831913141</v>
+      </c>
+      <c r="G69" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K69" t="b">
+        <v>0</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>(155, 31)</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>1.909457354621302</v>
+      </c>
+      <c r="O69" t="n">
+        <v>61</v>
+      </c>
+      <c r="P69" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>58</v>
+      </c>
+      <c r="R69" t="n">
+        <v>62</v>
+      </c>
+      <c r="S69" t="n">
+        <v>26</v>
+      </c>
+      <c r="T69" t="n">
+        <v>67</v>
+      </c>
+      <c r="U69" t="n">
+        <v>83</v>
+      </c>
+      <c r="V69" t="n">
+        <v>53.5483870967742</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>596</v>
+      </c>
+      <c r="B70" t="n">
+        <v>0.5243804518270906</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-0.04379025807871884</v>
+      </c>
+      <c r="D70" t="n">
+        <v>-0.08294660905330678</v>
+      </c>
+      <c r="E70" t="n">
+        <v>5.714977959515181</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.03687082554525924</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K70" t="b">
+        <v>1</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>(155, 14)</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>1.841986943282659</v>
+      </c>
+      <c r="O70" t="n">
+        <v>61</v>
+      </c>
+      <c r="P70" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>58</v>
+      </c>
+      <c r="R70" t="n">
+        <v>72</v>
+      </c>
+      <c r="S70" t="n">
+        <v>25</v>
+      </c>
+      <c r="T70" t="n">
+        <v>58</v>
+      </c>
+      <c r="U70" t="n">
+        <v>85</v>
+      </c>
+      <c r="V70" t="n">
+        <v>54.83870967741935</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>351</v>
+      </c>
+      <c r="B71" t="n">
+        <v>-0.1433819044790334</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-0.1335660390684636</v>
+      </c>
+      <c r="D71" t="n">
+        <v>-0.06747327441176841</v>
+      </c>
+      <c r="E71" t="n">
+        <v>5.657761759632663</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.03650168877182364</v>
+      </c>
+      <c r="G71" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K71" t="b">
+        <v>0</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>(155, 21)</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>1.273285702162011</v>
+      </c>
+      <c r="O71" t="n">
+        <v>61</v>
+      </c>
+      <c r="P71" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>58</v>
+      </c>
+      <c r="R71" t="n">
+        <v>52</v>
+      </c>
+      <c r="S71" t="n">
+        <v>63</v>
+      </c>
+      <c r="T71" t="n">
+        <v>40</v>
+      </c>
+      <c r="U71" t="n">
+        <v>74</v>
+      </c>
+      <c r="V71" t="n">
+        <v>47.74193548387097</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>557</v>
+      </c>
+      <c r="B72" t="n">
+        <v>0.4211056685493548</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-0.06407149883786559</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.01658475906281524</v>
+      </c>
+      <c r="E72" t="n">
+        <v>5.403637015056447</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.03486217429068676</v>
+      </c>
+      <c r="G72" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K72" t="b">
+        <v>0</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>(155, 48)</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>1.5441136062527</v>
+      </c>
+      <c r="O72" t="n">
+        <v>61</v>
+      </c>
+      <c r="P72" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>58</v>
+      </c>
+      <c r="R72" t="n">
+        <v>63</v>
+      </c>
+      <c r="S72" t="n">
+        <v>22</v>
+      </c>
+      <c r="T72" t="n">
+        <v>70</v>
+      </c>
+      <c r="U72" t="n">
+        <v>84</v>
+      </c>
+      <c r="V72" t="n">
+        <v>54.19354838709678</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B73" t="n">
+        <v>-0.01324886211416072</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0.0110467719931458</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.04025981452611916</v>
+      </c>
+      <c r="E73" t="n">
+        <v>5.237545341456908</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.0337906151061736</v>
+      </c>
+      <c r="G73" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K73" t="b">
+        <v>0</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>(155, 31)</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>2.058867796596119</v>
+      </c>
+      <c r="O73" t="n">
+        <v>61</v>
+      </c>
+      <c r="P73" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>58</v>
+      </c>
+      <c r="R73" t="n">
         <v>80</v>
       </c>
-      <c r="V11" t="n">
-        <v>52.63157894736842</v>
+      <c r="S73" t="n">
+        <v>23</v>
+      </c>
+      <c r="T73" t="n">
+        <v>52</v>
+      </c>
+      <c r="U73" t="n">
+        <v>85</v>
+      </c>
+      <c r="V73" t="n">
+        <v>54.83870967741935</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>478</v>
+      </c>
+      <c r="B74" t="n">
+        <v>0.09133044372469498</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-0.1681757217905043</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.04002280960124618</v>
+      </c>
+      <c r="E74" t="n">
+        <v>5.16693000309175</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.03333503227801129</v>
+      </c>
+      <c r="G74" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K74" t="b">
+        <v>1</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>(155, 49)</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>1.198215485107515</v>
+      </c>
+      <c r="O74" t="n">
+        <v>61</v>
+      </c>
+      <c r="P74" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>58</v>
+      </c>
+      <c r="R74" t="n">
+        <v>79</v>
+      </c>
+      <c r="S74" t="n">
+        <v>25</v>
+      </c>
+      <c r="T74" t="n">
+        <v>51</v>
+      </c>
+      <c r="U74" t="n">
+        <v>83</v>
+      </c>
+      <c r="V74" t="n">
+        <v>53.5483870967742</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>330</v>
+      </c>
+      <c r="B75" t="n">
+        <v>0.07977243874430712</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0.007900199376845763</v>
+      </c>
+      <c r="D75" t="n">
+        <v>-0.005858573511656477</v>
+      </c>
+      <c r="E75" t="n">
+        <v>5.015614253311554</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.03235880163426809</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K75" t="b">
+        <v>0</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>(155, 97)</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>3.09594746799766</v>
+      </c>
+      <c r="O75" t="n">
+        <v>61</v>
+      </c>
+      <c r="P75" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>58</v>
+      </c>
+      <c r="R75" t="n">
+        <v>78</v>
+      </c>
+      <c r="S75" t="n">
+        <v>8</v>
+      </c>
+      <c r="T75" t="n">
+        <v>69</v>
+      </c>
+      <c r="U75" t="n">
+        <v>85</v>
+      </c>
+      <c r="V75" t="n">
+        <v>54.83870967741935</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>633</v>
+      </c>
+      <c r="B76" t="n">
+        <v>0.3703600357627491</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-0.03276215348126968</v>
+      </c>
+      <c r="D76" t="n">
+        <v>-0.04226829482841566</v>
+      </c>
+      <c r="E76" t="n">
+        <v>4.922175628552438</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.0317559717971125</v>
+      </c>
+      <c r="G76" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K76" t="b">
+        <v>0</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>(155, 40)</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>1.96928829221399</v>
+      </c>
+      <c r="O76" t="n">
+        <v>61</v>
+      </c>
+      <c r="P76" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>58</v>
+      </c>
+      <c r="R76" t="n">
+        <v>54</v>
+      </c>
+      <c r="S76" t="n">
+        <v>54</v>
+      </c>
+      <c r="T76" t="n">
+        <v>47</v>
+      </c>
+      <c r="U76" t="n">
+        <v>76</v>
+      </c>
+      <c r="V76" t="n">
+        <v>49.03225806451613</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>215</v>
+      </c>
+      <c r="B77" t="n">
+        <v>0.004208643854292973</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-0.1471783066653532</v>
+      </c>
+      <c r="D77" t="n">
+        <v>-0.06031708359855514</v>
+      </c>
+      <c r="E77" t="n">
+        <v>4.763577177288894</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.03073275598250899</v>
+      </c>
+      <c r="G77" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K77" t="b">
+        <v>0</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>(155, 16)</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>1.208813083115487</v>
+      </c>
+      <c r="O77" t="n">
+        <v>61</v>
+      </c>
+      <c r="P77" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>58</v>
+      </c>
+      <c r="R77" t="n">
+        <v>69</v>
+      </c>
+      <c r="S77" t="n">
+        <v>9</v>
+      </c>
+      <c r="T77" t="n">
+        <v>77</v>
+      </c>
+      <c r="U77" t="n">
+        <v>83</v>
+      </c>
+      <c r="V77" t="n">
+        <v>53.5483870967742</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>223</v>
+      </c>
+      <c r="B78" t="n">
+        <v>0.3919525432816471</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0.02651803335201393</v>
+      </c>
+      <c r="D78" t="n">
+        <v>-0.01597185770178925</v>
+      </c>
+      <c r="E78" t="n">
+        <v>4.709609528494866</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.03038457760319268</v>
+      </c>
+      <c r="G78" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K78" t="b">
+        <v>0</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>(155, 15)</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>0.1458081072548733</v>
+      </c>
+      <c r="O78" t="n">
+        <v>61</v>
+      </c>
+      <c r="P78" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>58</v>
+      </c>
+      <c r="R78" t="n">
+        <v>62</v>
+      </c>
+      <c r="S78" t="n">
+        <v>35</v>
+      </c>
+      <c r="T78" t="n">
+        <v>58</v>
+      </c>
+      <c r="U78" t="n">
+        <v>79</v>
+      </c>
+      <c r="V78" t="n">
+        <v>50.96774193548386</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>643</v>
+      </c>
+      <c r="B79" t="n">
+        <v>0.1940004837069534</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-0.1139781767241617</v>
+      </c>
+      <c r="D79" t="n">
+        <v>-0.05480597966477622</v>
+      </c>
+      <c r="E79" t="n">
+        <v>4.326028978970911</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.02790986438045749</v>
+      </c>
+      <c r="G79" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K79" t="b">
+        <v>0</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>(155, 25)</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>1.244870247819476</v>
+      </c>
+      <c r="O79" t="n">
+        <v>61</v>
+      </c>
+      <c r="P79" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>58</v>
+      </c>
+      <c r="R79" t="n">
+        <v>79</v>
+      </c>
+      <c r="S79" t="n">
+        <v>11</v>
+      </c>
+      <c r="T79" t="n">
+        <v>65</v>
+      </c>
+      <c r="U79" t="n">
+        <v>85</v>
+      </c>
+      <c r="V79" t="n">
+        <v>54.83870967741935</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>204</v>
+      </c>
+      <c r="B80" t="n">
+        <v>0.9485424779607621</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-0.005016051561817392</v>
+      </c>
+      <c r="D80" t="n">
+        <v>-0.08828311431856378</v>
+      </c>
+      <c r="E80" t="n">
+        <v>4.098772139160857</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.02644369122039263</v>
+      </c>
+      <c r="G80" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K80" t="b">
+        <v>1</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>(155, 37)</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>6.271814074178232</v>
+      </c>
+      <c r="O80" t="n">
+        <v>61</v>
+      </c>
+      <c r="P80" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>58</v>
+      </c>
+      <c r="R80" t="n">
+        <v>67</v>
+      </c>
+      <c r="S80" t="n">
+        <v>22</v>
+      </c>
+      <c r="T80" t="n">
+        <v>66</v>
+      </c>
+      <c r="U80" t="n">
+        <v>84</v>
+      </c>
+      <c r="V80" t="n">
+        <v>54.19354838709678</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>347</v>
+      </c>
+      <c r="B81" t="n">
+        <v>0.3892725854841763</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-0.005887297502431181</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.04094957361167768</v>
+      </c>
+      <c r="E81" t="n">
+        <v>4.037227370373444</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.0260466281959577</v>
+      </c>
+      <c r="G81" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K81" t="b">
+        <v>0</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>(155, 62)</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>5.42420791291788</v>
+      </c>
+      <c r="O81" t="n">
+        <v>61</v>
+      </c>
+      <c r="P81" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>58</v>
+      </c>
+      <c r="R81" t="n">
+        <v>65</v>
+      </c>
+      <c r="S81" t="n">
+        <v>23</v>
+      </c>
+      <c r="T81" t="n">
+        <v>67</v>
+      </c>
+      <c r="U81" t="n">
+        <v>82</v>
+      </c>
+      <c r="V81" t="n">
+        <v>52.90322580645162</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="n">
+        <v>-0.1854673448552981</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-0.04758961444179875</v>
+      </c>
+      <c r="D82" t="n">
+        <v>-0.01535531345372505</v>
+      </c>
+      <c r="E82" t="n">
+        <v>3.830911440360254</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.02471555767974357</v>
+      </c>
+      <c r="G82" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K82" t="b">
+        <v>0</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>(155, 16)</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>1.519347718397052</v>
+      </c>
+      <c r="O82" t="n">
+        <v>61</v>
+      </c>
+      <c r="P82" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>58</v>
+      </c>
+      <c r="R82" t="n">
+        <v>64</v>
+      </c>
+      <c r="S82" t="n">
+        <v>50</v>
+      </c>
+      <c r="T82" t="n">
+        <v>41</v>
+      </c>
+      <c r="U82" t="n">
+        <v>78</v>
+      </c>
+      <c r="V82" t="n">
+        <v>50.32258064516129</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>157</v>
+      </c>
+      <c r="B83" t="n">
+        <v>-0.02397554684132757</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-0.02812843797488853</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0.009313798975250242</v>
+      </c>
+      <c r="E83" t="n">
+        <v>3.018230967785399</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.01947245785668</v>
+      </c>
+      <c r="G83" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K83" t="b">
+        <v>1</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>(155, 22)</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>1.692269434728793</v>
+      </c>
+      <c r="O83" t="n">
+        <v>61</v>
+      </c>
+      <c r="P83" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>58</v>
+      </c>
+      <c r="R83" t="n">
+        <v>66</v>
+      </c>
+      <c r="S83" t="n">
+        <v>62</v>
+      </c>
+      <c r="T83" t="n">
+        <v>27</v>
+      </c>
+      <c r="U83" t="n">
+        <v>73</v>
+      </c>
+      <c r="V83" t="n">
+        <v>47.09677419354838</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>103</v>
+      </c>
+      <c r="B84" t="n">
+        <v>0.1248208760771899</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-0.09061001569131377</v>
+      </c>
+      <c r="D84" t="n">
+        <v>-0.01843937060730156</v>
+      </c>
+      <c r="E84" t="n">
+        <v>2.484638316852994</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.01602992462485802</v>
+      </c>
+      <c r="G84" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K84" t="b">
+        <v>0</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>(155, 17)</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>1.176911178113776</v>
+      </c>
+      <c r="O84" t="n">
+        <v>61</v>
+      </c>
+      <c r="P84" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>58</v>
+      </c>
+      <c r="R84" t="n">
+        <v>66</v>
+      </c>
+      <c r="S84" t="n">
+        <v>23</v>
+      </c>
+      <c r="T84" t="n">
+        <v>66</v>
+      </c>
+      <c r="U84" t="n">
+        <v>84</v>
+      </c>
+      <c r="V84" t="n">
+        <v>54.19354838709678</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p4_modeling/2024-10-13/df_best_model.xlsx
+++ b/data/germany/p4_modeling/2024-10-13/df_best_model.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V40"/>
+  <dimension ref="A1:V43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>% ROI 100</t>
+          <t>% roi_100</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -537,25 +537,25 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>569</v>
+        <v>372</v>
       </c>
       <c r="B2" t="n">
-        <v>2.467492115332216</v>
+        <v>19.58843435200377</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8474376968746554</v>
+        <v>12.08978366905407</v>
       </c>
       <c r="D2" t="n">
-        <v>2.293515387453079</v>
+        <v>8.923646245392932</v>
       </c>
       <c r="E2" t="n">
-        <v>998.564650363514</v>
+        <v>2237.514696383653</v>
       </c>
       <c r="F2" t="n">
-        <v>6.088808843679963</v>
+        <v>12.93361096175522</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -573,60 +573,60 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>(164, 31)</t>
+          <t>(173, 31)</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>neural_networ</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>6.184963409269436</v>
+        <v>0.06979672389515738</v>
       </c>
       <c r="O2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P2" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R2" t="n">
         <v>74</v>
       </c>
       <c r="S2" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="T2" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="U2" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V2" t="n">
-        <v>60.36585365853659</v>
+        <v>58.95953757225434</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>344</v>
+        <v>569</v>
       </c>
       <c r="B3" t="n">
-        <v>8.719305014810013</v>
+        <v>1.805143026727589</v>
       </c>
       <c r="C3" t="n">
-        <v>2.09105137514204</v>
+        <v>0.399552893388798</v>
       </c>
       <c r="D3" t="n">
-        <v>1.040248222325487</v>
+        <v>1.674107054453184</v>
       </c>
       <c r="E3" t="n">
-        <v>572.0722086097975</v>
+        <v>1243.894172710339</v>
       </c>
       <c r="F3" t="n">
-        <v>3.488245174449985</v>
+        <v>7.190139726649357</v>
       </c>
       <c r="G3" t="n">
         <v>-0.5</v>
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -647,134 +647,134 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>(164, 16)</t>
+          <t>(173, 31)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>neural_networ</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.6681776525997777</v>
+        <v>16.99546404398768</v>
       </c>
       <c r="O3" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P3" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R3" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S3" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="T3" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="U3" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="V3" t="n">
-        <v>59.7560975609756</v>
+        <v>60.11560693641619</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>415</v>
+        <v>287</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1058672525779005</v>
+        <v>1.514533543794844</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1758626280461979</v>
+        <v>1.12222635466451</v>
       </c>
       <c r="D4" t="n">
-        <v>1.241495438503277</v>
+        <v>0.03239924318880422</v>
       </c>
       <c r="E4" t="n">
-        <v>374.1004772244978</v>
+        <v>452.4052670475621</v>
       </c>
       <c r="F4" t="n">
-        <v>2.281100470881084</v>
+        <v>2.615059347095735</v>
       </c>
       <c r="G4" t="n">
         <v>-0.5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>kelly</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>(164, 9)</t>
+          <t>(173, 25)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>neural_networ</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>13.97092222619268</v>
+        <v>1.330242322528157</v>
       </c>
       <c r="O4" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P4" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R4" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="S4" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="T4" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U4" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="V4" t="n">
-        <v>58.53658536585365</v>
+        <v>57.22543352601156</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>96</v>
+        <v>415</v>
       </c>
       <c r="B5" t="n">
-        <v>2.9146544190515</v>
+        <v>0.7781545160500349</v>
       </c>
       <c r="C5" t="n">
-        <v>0.423410846337454</v>
+        <v>-0.1389666738869776</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5931283938396326</v>
+        <v>1.472920107039825</v>
       </c>
       <c r="E5" t="n">
-        <v>251.4968497302784</v>
+        <v>428.1802185086917</v>
       </c>
       <c r="F5" t="n">
-        <v>1.533517376404137</v>
+        <v>2.475030164790125</v>
       </c>
       <c r="G5" t="n">
         <v>-0.5</v>
@@ -795,7 +795,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>(164, 24)</t>
+          <t>(173, 9)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -804,125 +804,125 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.621818830739021</v>
+        <v>18.8102425247875</v>
       </c>
       <c r="O5" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P5" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R5" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S5" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="T5" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="U5" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="V5" t="n">
-        <v>59.7560975609756</v>
+        <v>58.38150289017341</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>51</v>
+        <v>464</v>
       </c>
       <c r="B6" t="n">
-        <v>1.582455512622571</v>
+        <v>4.283370314574909</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.4037199170186082</v>
+        <v>0.7418548293437999</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.01500682417045368</v>
+        <v>-0.1135558924479797</v>
       </c>
       <c r="E6" t="n">
-        <v>184.516271840327</v>
+        <v>419.8746510511403</v>
       </c>
       <c r="F6" t="n">
-        <v>1.125099218538579</v>
+        <v>2.427021104341851</v>
       </c>
       <c r="G6" t="n">
         <v>-0.25</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>kelly</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>(164, 26)</t>
+          <t>(173, 14)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>neural_networ</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.786831095297984</v>
+        <v>2.271558003455538</v>
       </c>
       <c r="O6" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P6" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R6" t="n">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="S6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T6" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="U6" t="n">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="V6" t="n">
-        <v>55.48780487804878</v>
+        <v>58.95953757225434</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>357</v>
+        <v>221</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1028684055647685</v>
+        <v>3.177363078042633</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5461457581108488</v>
+        <v>0.08223990188946416</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5556340631640611</v>
+        <v>0.2519465131128825</v>
       </c>
       <c r="E7" t="n">
-        <v>177.3779446179347</v>
+        <v>356.1664145603345</v>
       </c>
       <c r="F7" t="n">
-        <v>1.081572833036187</v>
+        <v>2.058765402082858</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5</v>
@@ -943,7 +943,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>(164, 49)</t>
+          <t>(173, 30)</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -952,51 +952,51 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0.9803739514107238</v>
+        <v>24.03365586269758</v>
       </c>
       <c r="O7" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P7" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q7" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R7" t="n">
         <v>80</v>
       </c>
       <c r="S7" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="T7" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="U7" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="V7" t="n">
-        <v>57.92682926829268</v>
+        <v>57.22543352601156</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>211</v>
+        <v>470</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.7170928334210607</v>
+        <v>5.404129895719989</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4914142800881285</v>
+        <v>1.123150699631763</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5812224880893888</v>
+        <v>0.8484415769630811</v>
       </c>
       <c r="E8" t="n">
-        <v>164.4605615666336</v>
+        <v>349.7576205093264</v>
       </c>
       <c r="F8" t="n">
-        <v>1.002808302235571</v>
+        <v>2.021720349764893</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5</v>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>(164, 46)</t>
+          <t>(173, 40)</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1026,54 +1026,54 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.040657634238327</v>
+        <v>0.8000437077835907</v>
       </c>
       <c r="O8" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P8" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R8" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="T8" t="n">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="U8" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="V8" t="n">
-        <v>58.53658536585365</v>
+        <v>56.64739884393064</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>180</v>
+        <v>392</v>
       </c>
       <c r="B9" t="n">
-        <v>5.315239545136007</v>
+        <v>-0.02144636107109591</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9093773533157713</v>
+        <v>-0.2777308649320975</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3907535682251925</v>
+        <v>-0.0224075926377202</v>
       </c>
       <c r="E9" t="n">
-        <v>154.6137046583615</v>
+        <v>252.4758205135219</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9427664918192773</v>
+        <v>1.459397806436542</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1091,67 +1091,67 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>(164, 35)</t>
+          <t>(173, 9)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>neural_networ</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.03671648340676457</v>
+        <v>6.254719553022495</v>
       </c>
       <c r="O9" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P9" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q9" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R9" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="T9" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="U9" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="V9" t="n">
-        <v>54.26829268292683</v>
+        <v>56.06936416184971</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>71</v>
+        <v>357</v>
       </c>
       <c r="B10" t="n">
-        <v>1.041064333830116</v>
+        <v>-0.1284042508783287</v>
       </c>
       <c r="C10" t="n">
-        <v>0.09945545533170062</v>
+        <v>0.708514120427854</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4038369974236006</v>
+        <v>0.7035910574786063</v>
       </c>
       <c r="E10" t="n">
-        <v>122.4992785322796</v>
+        <v>222.7730786687313</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7469468203187781</v>
+        <v>1.287705657044689</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>kelly</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1161,71 +1161,71 @@
         <v>0</v>
       </c>
       <c r="K10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>(164, 16)</t>
+          <t>(173, 49)</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>neural_networ</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>6.510365498077357</v>
+        <v>0.8174735265220623</v>
       </c>
       <c r="O10" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P10" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q10" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R10" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="S10" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="T10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="U10" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="V10" t="n">
-        <v>57.3170731707317</v>
+        <v>57.80346820809249</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>392</v>
+        <v>211</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.2328691936259068</v>
+        <v>-0.433036485325384</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.1497780250937248</v>
+        <v>0.4914202055972933</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1009170469403507</v>
+        <v>0.5812274460535993</v>
       </c>
       <c r="E11" t="n">
-        <v>120.3789162415775</v>
+        <v>216.451738627745</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7340177819608387</v>
+        <v>1.25116611923552</v>
       </c>
       <c r="G11" t="n">
         <v>-0.5</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>kelly</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1235,11 +1235,11 @@
         <v>0</v>
       </c>
       <c r="K11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>(164, 9)</t>
+          <t>(173, 46)</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1248,58 +1248,58 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>5.900704101963698</v>
+        <v>1.546020910383199</v>
       </c>
       <c r="O11" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P11" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q11" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R11" t="n">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="S11" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="T11" t="n">
         <v>54</v>
       </c>
       <c r="U11" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="V11" t="n">
-        <v>55.48780487804878</v>
+        <v>58.38150289017341</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>18</v>
+        <v>271</v>
       </c>
       <c r="B12" t="n">
-        <v>0.3251174465882732</v>
+        <v>3.877112251713984</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.1483837893755421</v>
+        <v>0.6359065801519886</v>
       </c>
       <c r="D12" t="n">
-        <v>0.09631564215125148</v>
+        <v>0.1601478716990745</v>
       </c>
       <c r="E12" t="n">
-        <v>116.5568716371844</v>
+        <v>192.7876405540399</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7107126319340514</v>
+        <v>1.114379425167861</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.35</v>
+        <v>-0.25</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>kelly</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1309,67 +1309,67 @@
         <v>0</v>
       </c>
       <c r="K12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>(164, 59)</t>
+          <t>(173, 16)</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>neural_networ</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>5.789691885650126</v>
+        <v>0.7524263153583221</v>
       </c>
       <c r="O12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P12" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R12" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="S12" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="T12" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="U12" t="n">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="V12" t="n">
-        <v>51.82926829268293</v>
+        <v>58.38150289017341</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>172</v>
+        <v>292</v>
       </c>
       <c r="B13" t="n">
-        <v>2.929119835416752</v>
+        <v>-0.894835748206571</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5801051395524126</v>
+        <v>-0.569811339293002</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2888511027666004</v>
+        <v>-0.1930371763530783</v>
       </c>
       <c r="E13" t="n">
-        <v>108.3882863662264</v>
+        <v>166.4970994496198</v>
       </c>
       <c r="F13" t="n">
-        <v>0.660904185159917</v>
+        <v>0.9624109794775714</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1387,67 +1387,67 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>(164, 25)</t>
+          <t>(173, 45)</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>neural_networ</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0.1392834507031707</v>
+        <v>2.688999346119877</v>
       </c>
       <c r="O13" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P13" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R13" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="T13" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="U13" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="V13" t="n">
-        <v>57.3170731707317</v>
+        <v>54.91329479768786</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>410</v>
+        <v>239</v>
       </c>
       <c r="B14" t="n">
-        <v>0.4708842879670061</v>
+        <v>0.1104950594801466</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0569622222440357</v>
+        <v>0.3143605843645559</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7476454741363654</v>
+        <v>0.00958283559509719</v>
       </c>
       <c r="E14" t="n">
-        <v>93.34916442158348</v>
+        <v>154.9180578372965</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5692022220828261</v>
+        <v>0.8954801031057603</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>kelly</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1457,11 +1457,11 @@
         <v>0</v>
       </c>
       <c r="K14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>(164, 33)</t>
+          <t>(173, 24)</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1470,58 +1470,58 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>8.992626685880836</v>
+        <v>1.848576277194138</v>
       </c>
       <c r="O14" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P14" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R14" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="S14" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="T14" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="U14" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="V14" t="n">
-        <v>53.65853658536586</v>
+        <v>57.22543352601156</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>406</v>
+        <v>649</v>
       </c>
       <c r="B15" t="n">
-        <v>0.2639743917591815</v>
+        <v>2.32597906071546</v>
       </c>
       <c r="C15" t="n">
-        <v>0.07202364687975148</v>
+        <v>-0.01575222786251857</v>
       </c>
       <c r="D15" t="n">
-        <v>0.09165325941108667</v>
+        <v>-0.03824815102129539</v>
       </c>
       <c r="E15" t="n">
-        <v>92.39146425866267</v>
+        <v>138.0617980965956</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5633625869430651</v>
+        <v>0.7980450757028648</v>
       </c>
       <c r="G15" t="n">
         <v>-0.5</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>kelly</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1531,67 +1531,67 @@
         <v>0</v>
       </c>
       <c r="K15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>(164, 31)</t>
+          <t>(173, 26)</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>neural_networ</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>6.821911432555455</v>
+        <v>51.66236234442511</v>
       </c>
       <c r="O15" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P15" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q15" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R15" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S15" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="T15" t="n">
         <v>55</v>
       </c>
       <c r="U15" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="V15" t="n">
-        <v>57.92682926829268</v>
+        <v>56.06936416184971</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>391</v>
+        <v>472</v>
       </c>
       <c r="B16" t="n">
-        <v>0.3891781167403338</v>
+        <v>0.7943166383761951</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3442930174706444</v>
+        <v>0.6897663092578799</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0486644513072117</v>
+        <v>-0.05679889076648238</v>
       </c>
       <c r="E16" t="n">
-        <v>85.3718504892515</v>
+        <v>132.3391142015062</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5205600639588506</v>
+        <v>0.7649659780433885</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>(164, 9)</t>
+          <t>(173, 20)</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1618,51 +1618,51 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0.5119681130426507</v>
+        <v>0.1090219510234068</v>
       </c>
       <c r="O16" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P16" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q16" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R16" t="n">
         <v>69</v>
       </c>
       <c r="S16" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="T16" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="U16" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="V16" t="n">
-        <v>54.87804878048781</v>
+        <v>56.64739884393064</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>436</v>
+        <v>256</v>
       </c>
       <c r="B17" t="n">
-        <v>0.0496851954467823</v>
+        <v>0.4162804058409972</v>
       </c>
       <c r="C17" t="n">
-        <v>0.01520817417426372</v>
+        <v>0.1653851613630185</v>
       </c>
       <c r="D17" t="n">
-        <v>0.122764954332349</v>
+        <v>0.05280517501329959</v>
       </c>
       <c r="E17" t="n">
-        <v>69.71662551105464</v>
+        <v>128.7880632051893</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4251013750674064</v>
+        <v>0.7444396717062965</v>
       </c>
       <c r="G17" t="n">
         <v>-0.5</v>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1683,63 +1683,63 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>(164, 41)</t>
+          <t>(173, 21)</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>neural_networ</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>26.95216376379954</v>
+        <v>3.501248271435066</v>
       </c>
       <c r="O17" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P17" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q17" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R17" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="S17" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="T17" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U17" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="V17" t="n">
-        <v>56.70731707317073</v>
+        <v>56.06936416184971</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="B18" t="n">
-        <v>0.35978066989485</v>
+        <v>-0.4575193305862163</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1184698887176634</v>
+        <v>-0.2623454723641808</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1254582611407204</v>
+        <v>-0.1885497792236935</v>
       </c>
       <c r="E18" t="n">
-        <v>65.27181819037651</v>
+        <v>128.0935478232385</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3979988914047348</v>
+        <v>0.7404251319262342</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1757,60 +1757,60 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>(164, 16)</t>
+          <t>(173, 16)</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>neural_networ</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.359494093501202</v>
+        <v>3.822328608356527</v>
       </c>
       <c r="O18" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P18" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q18" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R18" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="S18" t="n">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="T18" t="n">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="U18" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V18" t="n">
-        <v>56.09756097560976</v>
+        <v>53.75722543352601</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>212</v>
+        <v>51</v>
       </c>
       <c r="B19" t="n">
-        <v>1.009607135416648</v>
+        <v>1.956152183882032</v>
       </c>
       <c r="C19" t="n">
-        <v>0.03043779071563108</v>
+        <v>-0.2665480261455733</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.08102686566276901</v>
+        <v>0.1058991172631519</v>
       </c>
       <c r="E19" t="n">
-        <v>58.65144241916443</v>
+        <v>122.9331951317929</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3576307464583197</v>
+        <v>0.7105965036519821</v>
       </c>
       <c r="G19" t="n">
         <v>-0.25</v>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1831,60 +1831,60 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>(164, 46)</t>
+          <t>(173, 26)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>neural_networ</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>10.74956322551562</v>
+        <v>3.665922963030665</v>
       </c>
       <c r="O19" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P19" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R19" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S19" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="T19" t="n">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="U19" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="V19" t="n">
-        <v>53.65853658536586</v>
+        <v>54.91329479768786</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>256</v>
+        <v>406</v>
       </c>
       <c r="B20" t="n">
-        <v>0.6324919370335601</v>
+        <v>0.009532974193524524</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2156272001956313</v>
+        <v>0.07210239310945653</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1302237493621677</v>
+        <v>0.09170896231956456</v>
       </c>
       <c r="E20" t="n">
-        <v>56.59563872566952</v>
+        <v>117.2838225152167</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3450953580833507</v>
+        <v>0.677941170608189</v>
       </c>
       <c r="G20" t="n">
         <v>-0.5</v>
@@ -1905,60 +1905,60 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>(164, 21)</t>
+          <t>(173, 31)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>neural_networ</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0.6004259099513293</v>
+        <v>8.402478078349306</v>
       </c>
       <c r="O20" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P20" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q20" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R20" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="S20" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="T20" t="n">
         <v>60</v>
       </c>
       <c r="U20" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="V20" t="n">
-        <v>55.48780487804878</v>
+        <v>57.80346820809249</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>52</v>
+        <v>341</v>
       </c>
       <c r="B21" t="n">
-        <v>0.7136305794309601</v>
+        <v>-0.1488793778945157</v>
       </c>
       <c r="C21" t="n">
-        <v>0.05266689839799753</v>
+        <v>0.1774407185117813</v>
       </c>
       <c r="D21" t="n">
-        <v>0.09113161331867994</v>
+        <v>0.2781818689020167</v>
       </c>
       <c r="E21" t="n">
-        <v>55.40780600387669</v>
+        <v>114.2177839807231</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3378524756333945</v>
+        <v>0.6602184045128502</v>
       </c>
       <c r="G21" t="n">
         <v>-0.5</v>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>(164, 26)</t>
+          <t>(173, 31)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1988,72 +1988,72 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>5.414892198137116</v>
+        <v>2.72078297501379</v>
       </c>
       <c r="O21" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P21" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q21" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R21" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="T21" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="U21" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="V21" t="n">
-        <v>57.92682926829268</v>
+        <v>54.33526011560693</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>341</v>
+        <v>71</v>
       </c>
       <c r="B22" t="n">
-        <v>0.0639317898890755</v>
+        <v>0.6665947266203903</v>
       </c>
       <c r="C22" t="n">
-        <v>0.177440707222766</v>
+        <v>0.1644752561366362</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2781818598430387</v>
+        <v>0.415889472016633</v>
       </c>
       <c r="E22" t="n">
-        <v>52.33494320735846</v>
+        <v>78.39986976066933</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3191155073619418</v>
+        <v>0.4531784379229441</v>
       </c>
       <c r="G22" t="n">
         <v>-0.5</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>kelly</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>(164, 31)</t>
+          <t>(173, 16)</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2062,125 +2062,125 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0.7984346002482491</v>
+        <v>1.75529856932687</v>
       </c>
       <c r="O22" t="n">
+        <v>70</v>
+      </c>
+      <c r="P22" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>62</v>
+      </c>
+      <c r="R22" t="n">
+        <v>70</v>
+      </c>
+      <c r="S22" t="n">
+        <v>36</v>
+      </c>
+      <c r="T22" t="n">
         <v>67</v>
       </c>
-      <c r="P22" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>61</v>
-      </c>
-      <c r="R22" t="n">
-        <v>62</v>
-      </c>
-      <c r="S22" t="n">
-        <v>37</v>
-      </c>
-      <c r="T22" t="n">
-        <v>65</v>
-      </c>
       <c r="U22" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="V22" t="n">
-        <v>53.65853658536586</v>
+        <v>56.64739884393064</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>292</v>
+        <v>256</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.3869150481770663</v>
+        <v>-0.2514141712537941</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.3203013283574412</v>
+        <v>-0.01260782377674616</v>
       </c>
       <c r="D23" t="n">
-        <v>0.003948641259716226</v>
+        <v>-0.1829638442336605</v>
       </c>
       <c r="E23" t="n">
-        <v>42.4036447623179</v>
+        <v>70.11049330802183</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2585588095263286</v>
+        <v>0.4052629670983921</v>
       </c>
       <c r="G23" t="n">
         <v>-0.5</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>kelly</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>(164, 45)</t>
+          <t>(173, 21)</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>neural_networ</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.807236144952197</v>
+        <v>33.14376836753209</v>
       </c>
       <c r="O23" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P23" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q23" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R23" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="S23" t="n">
         <v>43</v>
       </c>
       <c r="T23" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="U23" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="V23" t="n">
-        <v>53.65853658536586</v>
+        <v>54.91329479768786</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>478</v>
+        <v>349</v>
       </c>
       <c r="B24" t="n">
-        <v>0.09099907916263589</v>
+        <v>0.6321214440933778</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.1682534848111366</v>
+        <v>-0.1177576634592376</v>
       </c>
       <c r="D24" t="n">
-        <v>0.03983405170965398</v>
+        <v>-0.1528526025036869</v>
       </c>
       <c r="E24" t="n">
-        <v>37.83751091251892</v>
+        <v>58.11164424658411</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2307165299543837</v>
+        <v>0.3359054580727405</v>
       </c>
       <c r="G24" t="n">
         <v>-0.5</v>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>(164, 49)</t>
+          <t>(173, 42)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2210,58 +2210,58 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.371243693486417</v>
+        <v>3.852514632213434</v>
       </c>
       <c r="O24" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P24" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q24" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R24" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="T24" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="U24" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="V24" t="n">
-        <v>55.48780487804878</v>
+        <v>54.91329479768786</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>103</v>
+        <v>478</v>
       </c>
       <c r="B25" t="n">
-        <v>0.1852971682899971</v>
+        <v>0.3015315041808052</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.2241771601071997</v>
+        <v>-0.168250968120963</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0952727885026409</v>
+        <v>0.03983618943236479</v>
       </c>
       <c r="E25" t="n">
-        <v>34.57771254663606</v>
+        <v>56.52464954882683</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2108397106502199</v>
+        <v>0.3267320783169181</v>
       </c>
       <c r="G25" t="n">
         <v>-0.5</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>kelly</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -2271,11 +2271,11 @@
         <v>0</v>
       </c>
       <c r="K25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>(164, 17)</t>
+          <t>(173, 49)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2284,105 +2284,105 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.940504869226633</v>
+        <v>2.941932827881359</v>
       </c>
       <c r="O25" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P25" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q25" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R25" t="n">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="S25" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="T25" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="U25" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="V25" t="n">
-        <v>56.09756097560976</v>
+        <v>55.49132947976878</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>277</v>
+        <v>246</v>
       </c>
       <c r="B26" t="n">
-        <v>0.5945303593742602</v>
+        <v>-0.2459324660089081</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1333491381957629</v>
+        <v>-0.2666030577598808</v>
       </c>
       <c r="D26" t="n">
-        <v>0.09798978438326288</v>
+        <v>-0.09162579118790176</v>
       </c>
       <c r="E26" t="n">
-        <v>30.47457314901002</v>
+        <v>52.18861142375334</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1858205679817684</v>
+        <v>0.3016682741257418</v>
       </c>
       <c r="G26" t="n">
         <v>-0.5</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>kelly</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>(164, 42)</t>
+          <t>(173, 33)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>neural_networ</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.393489080589144</v>
+        <v>2.13152593470043</v>
       </c>
       <c r="O26" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P26" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q26" t="n">
+        <v>62</v>
+      </c>
+      <c r="R26" t="n">
+        <v>69</v>
+      </c>
+      <c r="S26" t="n">
+        <v>43</v>
+      </c>
+      <c r="T26" t="n">
         <v>61</v>
       </c>
-      <c r="R26" t="n">
-        <v>68</v>
-      </c>
-      <c r="S26" t="n">
-        <v>36</v>
-      </c>
-      <c r="T26" t="n">
-        <v>60</v>
-      </c>
       <c r="U26" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="V26" t="n">
-        <v>54.26829268292683</v>
+        <v>54.33526011560693</v>
       </c>
     </row>
     <row r="27">
@@ -2390,19 +2390,19 @@
         <v>361</v>
       </c>
       <c r="B27" t="n">
-        <v>0.8393279727099684</v>
+        <v>1.683785216191931</v>
       </c>
       <c r="C27" t="n">
-        <v>0.08629291064338972</v>
+        <v>0.04808433295502482</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.06819410370837849</v>
+        <v>-0.162707348600144</v>
       </c>
       <c r="E27" t="n">
-        <v>26.37203420857547</v>
+        <v>49.62669263019785</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1608050866376553</v>
+        <v>0.2868594949722419</v>
       </c>
       <c r="G27" t="n">
         <v>-0.25</v>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>(164, 31)</t>
+          <t>(173, 31)</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2432,51 +2432,51 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0.8634796930444417</v>
+        <v>4.965758020196577</v>
       </c>
       <c r="O27" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P27" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q27" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R27" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="S27" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="T27" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="U27" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="V27" t="n">
-        <v>53.65853658536586</v>
+        <v>53.75722543352601</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>135</v>
+        <v>47</v>
       </c>
       <c r="B28" t="n">
-        <v>0.9084570868671136</v>
+        <v>-0.0274273594778802</v>
       </c>
       <c r="C28" t="n">
-        <v>0.08474959110538804</v>
+        <v>-0.1205499147405227</v>
       </c>
       <c r="D28" t="n">
-        <v>0.03114911204112398</v>
+        <v>-0.09316772297398557</v>
       </c>
       <c r="E28" t="n">
-        <v>25.28531590882059</v>
+        <v>45.71146535298951</v>
       </c>
       <c r="F28" t="n">
-        <v>0.154178755541589</v>
+        <v>0.264228123427685</v>
       </c>
       <c r="G28" t="n">
         <v>-0.5</v>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2497,60 +2497,60 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>(164, 21)</t>
+          <t>(173, 16)</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>neural_networ</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0.8192271317257945</v>
+        <v>3.191856576559361</v>
       </c>
       <c r="O28" t="n">
+        <v>70</v>
+      </c>
+      <c r="P28" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>62</v>
+      </c>
+      <c r="R28" t="n">
         <v>67</v>
       </c>
-      <c r="P28" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>61</v>
-      </c>
-      <c r="R28" t="n">
-        <v>78</v>
-      </c>
       <c r="S28" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="T28" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="U28" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="V28" t="n">
-        <v>56.70731707317073</v>
+        <v>54.33526011560693</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>365</v>
+        <v>277</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.3075668991949203</v>
+        <v>0.4217618165861737</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.06694295116943721</v>
+        <v>-0.1333491381957627</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.01803552550374178</v>
+        <v>0.09798978438326306</v>
       </c>
       <c r="E29" t="n">
-        <v>24.6829418272023</v>
+        <v>42.61575295046626</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1505057428487945</v>
+        <v>0.24633383208362</v>
       </c>
       <c r="G29" t="n">
         <v>-0.5</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>(164, 16)</t>
+          <t>(173, 42)</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2580,58 +2580,58 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>3.24826871566887</v>
+        <v>2.847284770014716</v>
       </c>
       <c r="O29" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P29" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q29" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R29" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="S29" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="T29" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="U29" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="V29" t="n">
-        <v>52.4390243902439</v>
+        <v>54.33526011560693</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>596</v>
+        <v>223</v>
       </c>
       <c r="B30" t="n">
-        <v>0.4229450075302327</v>
+        <v>0.7668767912127373</v>
       </c>
       <c r="C30" t="n">
-        <v>0.02538915130008746</v>
+        <v>-0.05794994201157323</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0434225429736379</v>
+        <v>-0.1114995105887111</v>
       </c>
       <c r="E30" t="n">
-        <v>22.66853237800871</v>
+        <v>41.85759908568795</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1382227584024921</v>
+        <v>0.2419514398016644</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>kelly</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -2641,11 +2641,11 @@
         <v>0</v>
       </c>
       <c r="K30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>(164, 14)</t>
+          <t>(173, 15)</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2654,51 +2654,51 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>4.444166162498545</v>
+        <v>5.175180015768507</v>
       </c>
       <c r="O30" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P30" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q30" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R30" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="T30" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="U30" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V30" t="n">
-        <v>56.70731707317073</v>
+        <v>53.17919075144508</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>557</v>
+        <v>410</v>
       </c>
       <c r="B31" t="n">
-        <v>0.8391531424333487</v>
+        <v>0.2885444446472729</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1753238846055852</v>
+        <v>0.1618757974671074</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.02098699888250953</v>
+        <v>0.5233444983361371</v>
       </c>
       <c r="E31" t="n">
-        <v>20.12828713927671</v>
+        <v>39.15961781684194</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1227334581663214</v>
+        <v>0.2263561723516875</v>
       </c>
       <c r="G31" t="n">
         <v>-0.25</v>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>(164, 48)</t>
+          <t>(173, 33)</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2728,54 +2728,54 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.700038437104145</v>
+        <v>0.3983323998615809</v>
       </c>
       <c r="O31" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P31" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q31" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R31" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="S31" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="T31" t="n">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="U31" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V31" t="n">
-        <v>55.48780487804878</v>
+        <v>52.02312138728323</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>347</v>
+        <v>212</v>
       </c>
       <c r="B32" t="n">
-        <v>0.7673333195138184</v>
+        <v>0.5834008384362699</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.06367469629444528</v>
+        <v>0.08792965626157936</v>
       </c>
       <c r="D32" t="n">
-        <v>0.02434669257554693</v>
+        <v>0.004462640734566889</v>
       </c>
       <c r="E32" t="n">
-        <v>19.9113432189498</v>
+        <v>36.85960828900795</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1214106293838402</v>
+        <v>0.2130613195896413</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>(164, 62)</t>
+          <t>(173, 46)</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2802,58 +2802,58 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.906732759625766</v>
+        <v>1.423088280429659</v>
       </c>
       <c r="O32" t="n">
+        <v>70</v>
+      </c>
+      <c r="P32" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>62</v>
+      </c>
+      <c r="R32" t="n">
         <v>67</v>
       </c>
-      <c r="P32" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>61</v>
-      </c>
-      <c r="R32" t="n">
-        <v>71</v>
-      </c>
       <c r="S32" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="T32" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="U32" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="V32" t="n">
-        <v>54.87804878048781</v>
+        <v>53.17919075144508</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>23</v>
+        <v>596</v>
       </c>
       <c r="B33" t="n">
-        <v>0.3606435220738905</v>
+        <v>0.3139745969227781</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1093745055151972</v>
+        <v>-0.04378893989475244</v>
       </c>
       <c r="D33" t="n">
-        <v>0.02637076678783255</v>
+        <v>-0.08294580436539434</v>
       </c>
       <c r="E33" t="n">
-        <v>19.46768085747156</v>
+        <v>30.99851429721406</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1187053710821437</v>
+        <v>0.1791821635677113</v>
       </c>
       <c r="G33" t="n">
         <v>-0.5</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>kelly</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -2863,71 +2863,71 @@
         <v>0</v>
       </c>
       <c r="K33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>(164, 15)</t>
+          <t>(173, 14)</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>neural_networ</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0.08531115658986917</v>
+        <v>5.091950250414353</v>
       </c>
       <c r="O33" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P33" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q33" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R33" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="S33" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="T33" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="U33" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="V33" t="n">
-        <v>53.65853658536586</v>
+        <v>56.64739884393064</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>223</v>
+        <v>332</v>
       </c>
       <c r="B34" t="n">
-        <v>0.7633101829805059</v>
+        <v>-0.0396979896206264</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.01370082227262955</v>
+        <v>-0.1228629298304986</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.08969011095594338</v>
+        <v>-0.1676279195316397</v>
       </c>
       <c r="E34" t="n">
-        <v>18.42101799279702</v>
+        <v>29.26563509689021</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1123232804438843</v>
+        <v>0.1691655207912729</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>kelly</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -2937,11 +2937,11 @@
         <v>0</v>
       </c>
       <c r="K34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>(164, 15)</t>
+          <t>(173, 73)</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2950,51 +2950,51 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>9.198287534046413</v>
+        <v>2.376863802813861</v>
       </c>
       <c r="O34" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P34" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q34" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R34" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="S34" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="T34" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="U34" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="V34" t="n">
-        <v>52.4390243902439</v>
+        <v>56.06936416184971</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>647</v>
+        <v>336</v>
       </c>
       <c r="B35" t="n">
-        <v>1.22921828743119</v>
+        <v>0.3471054863970255</v>
       </c>
       <c r="C35" t="n">
-        <v>0.04192348999652765</v>
+        <v>0.06631541303508399</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.03399802607863535</v>
+        <v>0.0005144660271629201</v>
       </c>
       <c r="E35" t="n">
-        <v>15.97570478283197</v>
+        <v>27.63111370405394</v>
       </c>
       <c r="F35" t="n">
-        <v>0.09741283404165835</v>
+        <v>0.1597174202546471</v>
       </c>
       <c r="G35" t="n">
         <v>-0.5</v>
@@ -3015,25 +3015,25 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>(164, 39)</t>
+          <t>(173, 25)</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>neural_networ</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.323585990806744</v>
+        <v>1.408450961017901</v>
       </c>
       <c r="O35" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P35" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q35" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R35" t="n">
         <v>66</v>
@@ -3042,36 +3042,36 @@
         <v>40</v>
       </c>
       <c r="T35" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="U35" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="V35" t="n">
-        <v>53.65853658536586</v>
+        <v>54.33526011560693</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>146</v>
+        <v>387</v>
       </c>
       <c r="B36" t="n">
-        <v>0.2789774486168881</v>
+        <v>-0.1126035349848848</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1826366090645074</v>
+        <v>0.1312974964212525</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.06900633864065933</v>
+        <v>-0.1203947805046827</v>
       </c>
       <c r="E36" t="n">
-        <v>14.88503680049649</v>
+        <v>27.20526605576363</v>
       </c>
       <c r="F36" t="n">
-        <v>0.09076241951522251</v>
+        <v>0.1572558731547031</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -3089,60 +3089,60 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>(164, 33)</t>
+          <t>(173, 25)</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>neural_networ</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.496956333016264</v>
+        <v>0.1977065628895636</v>
       </c>
       <c r="O36" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P36" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q36" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R36" t="n">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="S36" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="T36" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="U36" t="n">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="V36" t="n">
-        <v>48.78048780487805</v>
+        <v>56.64739884393064</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>578</v>
+        <v>419</v>
       </c>
       <c r="B37" t="n">
-        <v>1.105222133687525</v>
+        <v>-0.336433528542058</v>
       </c>
       <c r="C37" t="n">
-        <v>0.002475743289979135</v>
+        <v>0.06158879819938278</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.07775925021998205</v>
+        <v>0.01559134296049166</v>
       </c>
       <c r="E37" t="n">
-        <v>12.17811691740192</v>
+        <v>25.68339808273013</v>
       </c>
       <c r="F37" t="n">
-        <v>0.07425681047196295</v>
+        <v>0.1484589484550874</v>
       </c>
       <c r="G37" t="n">
         <v>-0.5</v>
@@ -3163,67 +3163,67 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>(164, 14)</t>
+          <t>(173, 36)</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>neural_networ</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>28.99374400913301</v>
+        <v>1.410486205210206</v>
       </c>
       <c r="O37" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P37" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q37" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R37" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="S37" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="T37" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="U37" t="n">
         <v>90</v>
       </c>
       <c r="V37" t="n">
-        <v>54.87804878048781</v>
+        <v>52.02312138728323</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>274</v>
+        <v>452</v>
       </c>
       <c r="B38" t="n">
-        <v>-0.526274503446156</v>
+        <v>-0.02430483798026501</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2843296203753657</v>
+        <v>0.02309750955575041</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0577556873039967</v>
+        <v>-0.1618108193915159</v>
       </c>
       <c r="E38" t="n">
-        <v>12.0913878967238</v>
+        <v>24.6845745548647</v>
       </c>
       <c r="F38" t="n">
-        <v>0.07372797498002319</v>
+        <v>0.142685402051241</v>
       </c>
       <c r="G38" t="n">
         <v>-0.5</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>kelly</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -3233,11 +3233,11 @@
         <v>0</v>
       </c>
       <c r="K38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>(164, 83)</t>
+          <t>(173, 71)</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3246,51 +3246,51 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.259304587691881</v>
+        <v>5.177523239327667</v>
       </c>
       <c r="O38" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P38" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q38" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R38" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="S38" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="T38" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U38" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="V38" t="n">
-        <v>54.87804878048781</v>
+        <v>54.91329479768786</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>214</v>
+        <v>647</v>
       </c>
       <c r="B39" t="n">
-        <v>0.3261798251364371</v>
+        <v>1.056132031956025</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.04135053182999087</v>
+        <v>0.04192348999652793</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.04807762408407863</v>
+        <v>-0.03399802607863516</v>
       </c>
       <c r="E39" t="n">
-        <v>9.711758194785915</v>
+        <v>24.63541566630704</v>
       </c>
       <c r="F39" t="n">
-        <v>0.05921803777308485</v>
+        <v>0.1424012466260522</v>
       </c>
       <c r="G39" t="n">
         <v>-0.5</v>
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3311,114 +3311,336 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>(164, 31)</t>
+          <t>(173, 39)</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>neural_networ</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.432098576544425</v>
+        <v>2.396693515684065</v>
       </c>
       <c r="O39" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P39" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q39" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R39" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="T39" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="U39" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="V39" t="n">
-        <v>54.87804878048781</v>
+        <v>53.75722543352601</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>69</v>
+        <v>274</v>
       </c>
       <c r="B40" t="n">
-        <v>0.2068353010553065</v>
+        <v>-0.7289311358087421</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.0841585880554112</v>
+        <v>-0.3371262769248096</v>
       </c>
       <c r="D40" t="n">
-        <v>0.001292599881612186</v>
+        <v>0.0720367042858578</v>
       </c>
       <c r="E40" t="n">
-        <v>8.691200696649787</v>
+        <v>23.6275065992956</v>
       </c>
       <c r="F40" t="n">
-        <v>0.05299512619908407</v>
+        <v>0.1365751826548879</v>
       </c>
       <c r="G40" t="n">
         <v>-0.5</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>10</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>(173, 83)</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>1.405115803789299</v>
+      </c>
+      <c r="O40" t="n">
+        <v>70</v>
+      </c>
+      <c r="P40" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>62</v>
+      </c>
+      <c r="R40" t="n">
+        <v>85</v>
+      </c>
+      <c r="S40" t="n">
+        <v>35</v>
+      </c>
+      <c r="T40" t="n">
+        <v>53</v>
+      </c>
+      <c r="U40" t="n">
+        <v>95</v>
+      </c>
+      <c r="V40" t="n">
+        <v>54.91329479768786</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>290</v>
+      </c>
+      <c r="B41" t="n">
+        <v>0.005465786218609878</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.09976961728792062</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-0.1348329026845081</v>
+      </c>
+      <c r="E41" t="n">
+        <v>18.25156675071538</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.1055003858422855</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I40" t="n">
-        <v>5</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="b">
-        <v>0</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>(164, 31)</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
+      <c r="I41" t="n">
+        <v>10</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="b">
+        <v>0</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>(173, 60)</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>2.057440017413585</v>
+      </c>
+      <c r="O41" t="n">
+        <v>70</v>
+      </c>
+      <c r="P41" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>62</v>
+      </c>
+      <c r="R41" t="n">
+        <v>75</v>
+      </c>
+      <c r="S41" t="n">
+        <v>46</v>
+      </c>
+      <c r="T41" t="n">
+        <v>52</v>
+      </c>
+      <c r="U41" t="n">
+        <v>90</v>
+      </c>
+      <c r="V41" t="n">
+        <v>52.02312138728323</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="B42" t="n">
+        <v>0.7691237266298754</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.0847495911053872</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.03114911204112398</v>
+      </c>
+      <c r="E42" t="n">
+        <v>16.14510446181065</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.09332430324746038</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>10</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>(173, 21)</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="N40" t="n">
-        <v>1.629705505089883</v>
-      </c>
-      <c r="O40" t="n">
-        <v>67</v>
-      </c>
-      <c r="P40" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>61</v>
-      </c>
-      <c r="R40" t="n">
-        <v>72</v>
-      </c>
-      <c r="S40" t="n">
-        <v>27</v>
-      </c>
-      <c r="T40" t="n">
-        <v>65</v>
-      </c>
-      <c r="U40" t="n">
-        <v>90</v>
-      </c>
-      <c r="V40" t="n">
-        <v>54.87804878048781</v>
+      <c r="N42" t="n">
+        <v>0.1011770325996077</v>
+      </c>
+      <c r="O42" t="n">
+        <v>70</v>
+      </c>
+      <c r="P42" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>62</v>
+      </c>
+      <c r="R42" t="n">
+        <v>80</v>
+      </c>
+      <c r="S42" t="n">
+        <v>29</v>
+      </c>
+      <c r="T42" t="n">
+        <v>64</v>
+      </c>
+      <c r="U42" t="n">
+        <v>97</v>
+      </c>
+      <c r="V42" t="n">
+        <v>56.06936416184971</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>146</v>
+      </c>
+      <c r="B43" t="n">
+        <v>-0.005286631078294874</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.1826366090645077</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-0.06900633864065971</v>
+      </c>
+      <c r="E43" t="n">
+        <v>15.84586802093714</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.09159461283778697</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>10</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>(173, 33)</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>1.501512885652818</v>
+      </c>
+      <c r="O43" t="n">
+        <v>70</v>
+      </c>
+      <c r="P43" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>62</v>
+      </c>
+      <c r="R43" t="n">
+        <v>76</v>
+      </c>
+      <c r="S43" t="n">
+        <v>42</v>
+      </c>
+      <c r="T43" t="n">
+        <v>55</v>
+      </c>
+      <c r="U43" t="n">
+        <v>84</v>
+      </c>
+      <c r="V43" t="n">
+        <v>48.55491329479769</v>
       </c>
     </row>
   </sheetData>
